--- a/AAII_Financials/Yearly/ERIC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ERIC_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>25639400</v>
+        <v>25479200</v>
       </c>
       <c r="E8" s="3">
-        <v>21935100</v>
+        <v>26272100</v>
       </c>
       <c r="F8" s="3">
-        <v>21942300</v>
+        <v>22476400</v>
       </c>
       <c r="G8" s="3">
-        <v>21453700</v>
+        <v>22483700</v>
       </c>
       <c r="H8" s="3">
-        <v>19907300</v>
+        <v>21983100</v>
       </c>
       <c r="I8" s="3">
-        <v>19391800</v>
+        <v>20398600</v>
       </c>
       <c r="J8" s="3">
+        <v>19870300</v>
+      </c>
+      <c r="K8" s="3">
         <v>20802200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>23348800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>25164800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>26775800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>23673100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>25760100</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>14923600</v>
+        <v>15378100</v>
       </c>
       <c r="E9" s="3">
-        <v>12396600</v>
+        <v>15291900</v>
       </c>
       <c r="F9" s="3">
-        <v>13024400</v>
+        <v>12702500</v>
       </c>
       <c r="G9" s="3">
-        <v>13412800</v>
+        <v>13345800</v>
       </c>
       <c r="H9" s="3">
-        <v>12907200</v>
+        <v>13743800</v>
       </c>
       <c r="I9" s="3">
-        <v>14371600</v>
+        <v>13225700</v>
       </c>
       <c r="J9" s="3">
+        <v>14726200</v>
+      </c>
+      <c r="K9" s="3">
         <v>14312800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>15018700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>15952900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>17469500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>16181800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>16710100</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>10715700</v>
+        <v>10101100</v>
       </c>
       <c r="E10" s="3">
-        <v>9538500</v>
+        <v>10980200</v>
       </c>
       <c r="F10" s="3">
-        <v>8917900</v>
+        <v>9773900</v>
       </c>
       <c r="G10" s="3">
-        <v>8040900</v>
+        <v>9137900</v>
       </c>
       <c r="H10" s="3">
-        <v>7000100</v>
+        <v>8239300</v>
       </c>
       <c r="I10" s="3">
-        <v>5020200</v>
+        <v>7172900</v>
       </c>
       <c r="J10" s="3">
+        <v>5144100</v>
+      </c>
+      <c r="K10" s="3">
         <v>6489400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>8330100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>9211900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>9306300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>7491300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>9049900</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,50 +873,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>4460800</v>
+        <v>4666500</v>
       </c>
       <c r="E12" s="3">
-        <v>3959700</v>
+        <v>4570900</v>
       </c>
       <c r="F12" s="3">
-        <v>3711000</v>
+        <v>4057400</v>
       </c>
       <c r="G12" s="3">
-        <v>3632400</v>
+        <v>3802600</v>
       </c>
       <c r="H12" s="3">
-        <v>3551700</v>
+        <v>3722100</v>
       </c>
       <c r="I12" s="3">
-        <v>3359500</v>
+        <v>3639300</v>
       </c>
       <c r="J12" s="3">
+        <v>3442400</v>
+      </c>
+      <c r="K12" s="3">
         <v>2728000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3103700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3974100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3693400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3323800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3641400</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -944,51 +960,57 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>288500</v>
+        <v>3716900</v>
       </c>
       <c r="E14" s="3">
-        <v>65300</v>
+        <v>295600</v>
       </c>
       <c r="F14" s="3">
-        <v>136300</v>
+        <v>67000</v>
       </c>
       <c r="G14" s="3">
-        <v>168500</v>
+        <v>139700</v>
       </c>
       <c r="H14" s="3">
-        <v>798600</v>
+        <v>172700</v>
       </c>
       <c r="I14" s="3">
-        <v>2451900</v>
+        <v>818300</v>
       </c>
       <c r="J14" s="3">
+        <v>2512400</v>
+      </c>
+      <c r="K14" s="3">
         <v>706600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>476600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>160700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>524400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>159400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>237600</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1028,9 +1050,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>23088100</v>
+        <v>27445700</v>
       </c>
       <c r="E17" s="3">
-        <v>18934400</v>
+        <v>23657900</v>
       </c>
       <c r="F17" s="3">
-        <v>19316600</v>
+        <v>19401700</v>
       </c>
       <c r="G17" s="3">
-        <v>20456300</v>
+        <v>19793300</v>
       </c>
       <c r="H17" s="3">
-        <v>19790100</v>
+        <v>20961100</v>
       </c>
       <c r="I17" s="3">
-        <v>22672200</v>
+        <v>20278400</v>
       </c>
       <c r="J17" s="3">
+        <v>23231700</v>
+      </c>
+      <c r="K17" s="3">
         <v>20312500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>21286900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>23309600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>24674400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>22586200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>23728100</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>2551200</v>
+        <v>-1966500</v>
       </c>
       <c r="E18" s="3">
-        <v>3000700</v>
+        <v>2614200</v>
       </c>
       <c r="F18" s="3">
-        <v>2625600</v>
+        <v>3074700</v>
       </c>
       <c r="G18" s="3">
-        <v>997500</v>
+        <v>2690400</v>
       </c>
       <c r="H18" s="3">
-        <v>117300</v>
+        <v>1022100</v>
       </c>
       <c r="I18" s="3">
-        <v>-3280400</v>
+        <v>120200</v>
       </c>
       <c r="J18" s="3">
+        <v>-3361400</v>
+      </c>
+      <c r="K18" s="3">
         <v>489800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2061900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1855200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2101400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1086900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2032000</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1146,218 +1178,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-92100</v>
+        <v>-23900</v>
       </c>
       <c r="E20" s="3">
-        <v>-149100</v>
+        <v>-94300</v>
       </c>
       <c r="F20" s="3">
-        <v>72400</v>
+        <v>-152800</v>
       </c>
       <c r="G20" s="3">
-        <v>13300</v>
+        <v>74200</v>
       </c>
       <c r="H20" s="3">
-        <v>-161300</v>
+        <v>13600</v>
       </c>
       <c r="I20" s="3">
-        <v>-17800</v>
+        <v>-165200</v>
       </c>
       <c r="J20" s="3">
+        <v>-18200</v>
+      </c>
+      <c r="K20" s="3">
         <v>-88600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-47800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>41900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>78300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>151500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>218800</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>3453000</v>
+        <v>-819600</v>
       </c>
       <c r="E21" s="3">
-        <v>3672300</v>
+        <v>3544900</v>
       </c>
       <c r="F21" s="3">
-        <v>3507400</v>
+        <v>3768400</v>
       </c>
       <c r="G21" s="3">
-        <v>1826000</v>
+        <v>3599500</v>
       </c>
       <c r="H21" s="3">
-        <v>640600</v>
+        <v>1876600</v>
       </c>
       <c r="I21" s="3">
-        <v>-2496900</v>
+        <v>661100</v>
       </c>
       <c r="J21" s="3">
+        <v>-2553200</v>
+      </c>
+      <c r="K21" s="3">
         <v>1243700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2953700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2983600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3371900</v>
       </c>
-      <c r="N21" s="3" t="s">
+      <c r="O21" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3277900</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>135600</v>
+        <v>265700</v>
       </c>
       <c r="E22" s="3">
-        <v>89800</v>
+        <v>138900</v>
       </c>
       <c r="F22" s="3">
-        <v>128700</v>
+        <v>92000</v>
       </c>
       <c r="G22" s="3">
-        <v>183500</v>
+        <v>131900</v>
       </c>
       <c r="H22" s="3">
-        <v>94100</v>
+        <v>188000</v>
       </c>
       <c r="I22" s="3">
-        <v>97000</v>
+        <v>96500</v>
       </c>
       <c r="J22" s="3">
+        <v>99400</v>
+      </c>
+      <c r="K22" s="3">
         <v>127900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>135000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>151900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>166300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>180200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>193700</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>2323600</v>
+        <v>-2256100</v>
       </c>
       <c r="E23" s="3">
-        <v>2761800</v>
+        <v>2380900</v>
       </c>
       <c r="F23" s="3">
-        <v>2569400</v>
+        <v>2829900</v>
       </c>
       <c r="G23" s="3">
-        <v>827300</v>
+        <v>2632800</v>
       </c>
       <c r="H23" s="3">
-        <v>-138100</v>
+        <v>847700</v>
       </c>
       <c r="I23" s="3">
-        <v>-3395200</v>
+        <v>-141500</v>
       </c>
       <c r="J23" s="3">
+        <v>-3478900</v>
+      </c>
+      <c r="K23" s="3">
         <v>273300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1879100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1745200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2013500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1058200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2057100</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>519000</v>
+        <v>269400</v>
       </c>
       <c r="E24" s="3">
-        <v>592000</v>
+        <v>531800</v>
       </c>
       <c r="F24" s="3">
-        <v>905400</v>
+        <v>606600</v>
       </c>
       <c r="G24" s="3">
-        <v>653600</v>
+        <v>927700</v>
       </c>
       <c r="H24" s="3">
-        <v>454400</v>
+        <v>669700</v>
       </c>
       <c r="I24" s="3">
-        <v>-332800</v>
+        <v>465700</v>
       </c>
       <c r="J24" s="3">
+        <v>-341000</v>
+      </c>
+      <c r="K24" s="3">
         <v>177700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>586200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>515300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>579900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>441100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>630300</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>1804600</v>
+        <v>-2525600</v>
       </c>
       <c r="E26" s="3">
-        <v>2169800</v>
+        <v>1849100</v>
       </c>
       <c r="F26" s="3">
-        <v>1664000</v>
+        <v>2223300</v>
       </c>
       <c r="G26" s="3">
-        <v>173700</v>
+        <v>1705000</v>
       </c>
       <c r="H26" s="3">
-        <v>-592600</v>
+        <v>178000</v>
       </c>
       <c r="I26" s="3">
-        <v>-3062300</v>
+        <v>-607200</v>
       </c>
       <c r="J26" s="3">
+        <v>-3137900</v>
+      </c>
+      <c r="K26" s="3">
         <v>95600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1292900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1230000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1433600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>617100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1426800</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>1767900</v>
+        <v>-2558700</v>
       </c>
       <c r="E27" s="3">
-        <v>2142800</v>
+        <v>1811500</v>
       </c>
       <c r="F27" s="3">
-        <v>1650700</v>
+        <v>2195600</v>
       </c>
       <c r="G27" s="3">
-        <v>209900</v>
+        <v>1691500</v>
       </c>
       <c r="H27" s="3">
-        <v>-616600</v>
+        <v>215100</v>
       </c>
       <c r="I27" s="3">
-        <v>-3075800</v>
+        <v>-631800</v>
       </c>
       <c r="J27" s="3">
+        <v>-3151700</v>
+      </c>
+      <c r="K27" s="3">
         <v>78700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1281200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1276900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1413700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>600200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1384300</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1565,9 +1625,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>92100</v>
+        <v>23900</v>
       </c>
       <c r="E32" s="3">
-        <v>149100</v>
+        <v>94300</v>
       </c>
       <c r="F32" s="3">
-        <v>-72400</v>
+        <v>152800</v>
       </c>
       <c r="G32" s="3">
-        <v>-13300</v>
+        <v>-74200</v>
       </c>
       <c r="H32" s="3">
-        <v>161300</v>
+        <v>-13600</v>
       </c>
       <c r="I32" s="3">
-        <v>17800</v>
+        <v>165200</v>
       </c>
       <c r="J32" s="3">
+        <v>18200</v>
+      </c>
+      <c r="K32" s="3">
         <v>88600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>47800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-41900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-78300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-151500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-218800</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>1767900</v>
+        <v>-2558700</v>
       </c>
       <c r="E33" s="3">
-        <v>2142800</v>
+        <v>1811500</v>
       </c>
       <c r="F33" s="3">
-        <v>1650700</v>
+        <v>2195600</v>
       </c>
       <c r="G33" s="3">
-        <v>209900</v>
+        <v>1691500</v>
       </c>
       <c r="H33" s="3">
-        <v>-616600</v>
+        <v>215100</v>
       </c>
       <c r="I33" s="3">
-        <v>-3075800</v>
+        <v>-631800</v>
       </c>
       <c r="J33" s="3">
+        <v>-3151700</v>
+      </c>
+      <c r="K33" s="3">
         <v>78700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1281200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1276900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1413700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>600200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1384300</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>1767900</v>
+        <v>-2558700</v>
       </c>
       <c r="E35" s="3">
-        <v>2142800</v>
+        <v>1811500</v>
       </c>
       <c r="F35" s="3">
-        <v>1650700</v>
+        <v>2195600</v>
       </c>
       <c r="G35" s="3">
-        <v>209900</v>
+        <v>1691500</v>
       </c>
       <c r="H35" s="3">
-        <v>-616600</v>
+        <v>215100</v>
       </c>
       <c r="I35" s="3">
-        <v>-3075800</v>
+        <v>-631800</v>
       </c>
       <c r="J35" s="3">
+        <v>-3151700</v>
+      </c>
+      <c r="K35" s="3">
         <v>78700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1281200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1276900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1413700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>600200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1384300</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1901,386 +1986,414 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>3620900</v>
+        <v>3404600</v>
       </c>
       <c r="E41" s="3">
-        <v>5103400</v>
+        <v>3710300</v>
       </c>
       <c r="F41" s="3">
-        <v>4117800</v>
+        <v>5229300</v>
       </c>
       <c r="G41" s="3">
-        <v>4256400</v>
+        <v>4219500</v>
       </c>
       <c r="H41" s="3">
-        <v>3624700</v>
+        <v>4361400</v>
       </c>
       <c r="I41" s="3">
-        <v>3388200</v>
+        <v>3714100</v>
       </c>
       <c r="J41" s="3">
+        <v>3471800</v>
+      </c>
+      <c r="K41" s="3">
         <v>6980700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2121100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3272800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3370100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4643800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4390500</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>824900</v>
+        <v>927300</v>
       </c>
       <c r="E42" s="3">
-        <v>1221000</v>
+        <v>845200</v>
       </c>
       <c r="F42" s="3">
-        <v>643900</v>
+        <v>1251200</v>
       </c>
       <c r="G42" s="3">
-        <v>638200</v>
+        <v>659800</v>
       </c>
       <c r="H42" s="3">
-        <v>625500</v>
+        <v>653900</v>
       </c>
       <c r="I42" s="3">
-        <v>633800</v>
+        <v>641000</v>
       </c>
       <c r="J42" s="3">
+        <v>649500</v>
+      </c>
+      <c r="K42" s="3">
         <v>1258100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4145400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4692100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>5707900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>3328500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>4752600</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>7248800</v>
+        <v>6734800</v>
       </c>
       <c r="E43" s="3">
-        <v>6574100</v>
+        <v>7427700</v>
       </c>
       <c r="F43" s="3">
-        <v>6366800</v>
+        <v>6736300</v>
       </c>
       <c r="G43" s="3">
-        <v>6537700</v>
+        <v>6523900</v>
       </c>
       <c r="H43" s="3">
-        <v>7943100</v>
+        <v>6699100</v>
       </c>
       <c r="I43" s="3">
-        <v>13760800</v>
+        <v>8139100</v>
       </c>
       <c r="J43" s="3">
+        <v>14100300</v>
+      </c>
+      <c r="K43" s="3">
         <v>16876900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8365800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>10287500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9880400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>8527800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>9211600</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>4328800</v>
+        <v>3490100</v>
       </c>
       <c r="E44" s="3">
-        <v>3320200</v>
+        <v>4435600</v>
       </c>
       <c r="F44" s="3">
-        <v>2652900</v>
+        <v>3402100</v>
       </c>
       <c r="G44" s="3">
-        <v>2914100</v>
+        <v>2718400</v>
       </c>
       <c r="H44" s="3">
-        <v>2762300</v>
+        <v>2986000</v>
       </c>
       <c r="I44" s="3">
-        <v>2412100</v>
+        <v>2830400</v>
       </c>
       <c r="J44" s="3">
+        <v>2471700</v>
+      </c>
+      <c r="K44" s="3">
         <v>5847000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2688900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3110000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2680100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2993400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3754100</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>387100</v>
+        <v>438400</v>
       </c>
       <c r="E45" s="3">
-        <v>286400</v>
+        <v>396700</v>
       </c>
       <c r="F45" s="3">
-        <v>362100</v>
+        <v>293400</v>
       </c>
       <c r="G45" s="3">
-        <v>186200</v>
+        <v>371000</v>
       </c>
       <c r="H45" s="3">
-        <v>261800</v>
+        <v>190800</v>
       </c>
       <c r="I45" s="3">
-        <v>386300</v>
+        <v>268300</v>
       </c>
       <c r="J45" s="3">
+        <v>395800</v>
+      </c>
+      <c r="K45" s="3">
         <v>660300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>600300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>911100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>841400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>591500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>460800</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>16410500</v>
+        <v>14995100</v>
       </c>
       <c r="E46" s="3">
-        <v>16505100</v>
+        <v>16815400</v>
       </c>
       <c r="F46" s="3">
-        <v>14143600</v>
+        <v>16912400</v>
       </c>
       <c r="G46" s="3">
-        <v>14532600</v>
+        <v>14492700</v>
       </c>
       <c r="H46" s="3">
-        <v>15217400</v>
+        <v>14891200</v>
       </c>
       <c r="I46" s="3">
-        <v>14486200</v>
+        <v>15592900</v>
       </c>
       <c r="J46" s="3">
+        <v>14843700</v>
+      </c>
+      <c r="K46" s="3">
         <v>16532700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>17921500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>22273500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>22479900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>20084900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>22569600</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>1852400</v>
+        <v>2019100</v>
       </c>
       <c r="E47" s="3">
-        <v>3834400</v>
+        <v>1898100</v>
       </c>
       <c r="F47" s="3">
-        <v>2876900</v>
+        <v>3929000</v>
       </c>
       <c r="G47" s="3">
-        <v>2948500</v>
+        <v>2947900</v>
       </c>
       <c r="H47" s="3">
-        <v>3195800</v>
+        <v>3021200</v>
       </c>
       <c r="I47" s="3">
-        <v>3304400</v>
+        <v>3274700</v>
       </c>
       <c r="J47" s="3">
+        <v>3386000</v>
+      </c>
+      <c r="K47" s="3">
         <v>1940600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>889400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1177200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1111400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>881500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1553100</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>2087200</v>
+        <v>1791300</v>
       </c>
       <c r="E48" s="3">
-        <v>2032700</v>
+        <v>2138800</v>
       </c>
       <c r="F48" s="3">
-        <v>2017100</v>
+        <v>2082800</v>
       </c>
       <c r="G48" s="3">
-        <v>2109100</v>
+        <v>2066900</v>
       </c>
       <c r="H48" s="3">
-        <v>1213200</v>
+        <v>2161100</v>
       </c>
       <c r="I48" s="3">
-        <v>1214000</v>
+        <v>1243100</v>
       </c>
       <c r="J48" s="3">
+        <v>1243900</v>
+      </c>
+      <c r="K48" s="3">
         <v>3160000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1503600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1472600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1346400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1194500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1224700</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>10821900</v>
+        <v>7768000</v>
       </c>
       <c r="E49" s="3">
-        <v>4302000</v>
+        <v>11089000</v>
       </c>
       <c r="F49" s="3">
-        <v>4117400</v>
+        <v>4408100</v>
       </c>
       <c r="G49" s="3">
-        <v>3562600</v>
+        <v>4219000</v>
       </c>
       <c r="H49" s="3">
-        <v>3564000</v>
+        <v>3650500</v>
       </c>
       <c r="I49" s="3">
-        <v>3451600</v>
+        <v>3651900</v>
       </c>
       <c r="J49" s="3">
+        <v>3536800</v>
+      </c>
+      <c r="K49" s="3">
         <v>11181200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5285500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6008400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5618000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5138900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4999900</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>1831200</v>
+        <v>2164800</v>
       </c>
       <c r="E52" s="3">
-        <v>2182000</v>
+        <v>1876400</v>
       </c>
       <c r="F52" s="3">
-        <v>2482900</v>
+        <v>2235800</v>
       </c>
       <c r="G52" s="3">
-        <v>2943400</v>
+        <v>2544100</v>
       </c>
       <c r="H52" s="3">
-        <v>2186000</v>
+        <v>3016100</v>
       </c>
       <c r="I52" s="3">
-        <v>2081900</v>
+        <v>2240000</v>
       </c>
       <c r="J52" s="3">
+        <v>2133200</v>
+      </c>
+      <c r="K52" s="3">
         <v>1605000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1289300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1471300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1144200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1280500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1478000</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>33003300</v>
+        <v>28738200</v>
       </c>
       <c r="E54" s="3">
-        <v>28856100</v>
+        <v>33817700</v>
       </c>
       <c r="F54" s="3">
-        <v>25637900</v>
+        <v>29568200</v>
       </c>
       <c r="G54" s="3">
-        <v>26096100</v>
+        <v>26270500</v>
       </c>
       <c r="H54" s="3">
-        <v>25376400</v>
+        <v>26740100</v>
       </c>
       <c r="I54" s="3">
-        <v>24538100</v>
+        <v>26002600</v>
       </c>
       <c r="J54" s="3">
+        <v>25143600</v>
+      </c>
+      <c r="K54" s="3">
         <v>26829400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>26889400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>32402900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>31699800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>28580300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>31825200</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2525,260 +2654,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>3629200</v>
+        <v>2686600</v>
       </c>
       <c r="E57" s="3">
-        <v>3369300</v>
+        <v>3718800</v>
       </c>
       <c r="F57" s="3">
-        <v>3020300</v>
+        <v>3452400</v>
       </c>
       <c r="G57" s="3">
-        <v>2870700</v>
+        <v>3094800</v>
       </c>
       <c r="H57" s="3">
-        <v>2821600</v>
+        <v>2941500</v>
       </c>
       <c r="I57" s="3">
-        <v>2485100</v>
+        <v>2891200</v>
       </c>
       <c r="J57" s="3">
+        <v>2546500</v>
+      </c>
+      <c r="K57" s="3">
         <v>4830700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2117100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2701300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2414300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>11600</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>799700</v>
+        <v>1924400</v>
       </c>
       <c r="E58" s="3">
-        <v>1115500</v>
+        <v>819500</v>
       </c>
       <c r="F58" s="3">
-        <v>957200</v>
+        <v>1143000</v>
       </c>
       <c r="G58" s="3">
-        <v>1107200</v>
+        <v>980900</v>
       </c>
       <c r="H58" s="3">
-        <v>212900</v>
+        <v>1134500</v>
       </c>
       <c r="I58" s="3">
-        <v>240300</v>
+        <v>218200</v>
       </c>
       <c r="J58" s="3">
+        <v>246200</v>
+      </c>
+      <c r="K58" s="3">
         <v>1517000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>224700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>251800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>870000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>495600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>881500</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>9320500</v>
+        <v>7908400</v>
       </c>
       <c r="E59" s="3">
-        <v>7502000</v>
+        <v>9550500</v>
       </c>
       <c r="F59" s="3">
-        <v>6816600</v>
+        <v>7687200</v>
       </c>
       <c r="G59" s="3">
-        <v>7052200</v>
+        <v>6984800</v>
       </c>
       <c r="H59" s="3">
-        <v>7438000</v>
+        <v>7226300</v>
       </c>
       <c r="I59" s="3">
-        <v>9227600</v>
+        <v>7621600</v>
       </c>
       <c r="J59" s="3">
+        <v>9455300</v>
+      </c>
+      <c r="K59" s="3">
         <v>11607000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5893500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>8175800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7472300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9619100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10121700</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>13749400</v>
+        <v>12519400</v>
       </c>
       <c r="E60" s="3">
-        <v>11986800</v>
+        <v>14088700</v>
       </c>
       <c r="F60" s="3">
-        <v>10794100</v>
+        <v>12282600</v>
       </c>
       <c r="G60" s="3">
-        <v>11030000</v>
+        <v>11060500</v>
       </c>
       <c r="H60" s="3">
-        <v>10472500</v>
+        <v>11302200</v>
       </c>
       <c r="I60" s="3">
-        <v>9397500</v>
+        <v>10730900</v>
       </c>
       <c r="J60" s="3">
+        <v>9629400</v>
+      </c>
+      <c r="K60" s="3">
         <v>9517800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8235200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11129000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10756700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10123200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11014700</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>3188000</v>
+        <v>3331900</v>
       </c>
       <c r="E61" s="3">
-        <v>2768400</v>
+        <v>3266700</v>
       </c>
       <c r="F61" s="3">
-        <v>2768600</v>
+        <v>2836700</v>
       </c>
       <c r="G61" s="3">
-        <v>3385100</v>
+        <v>2836900</v>
       </c>
       <c r="H61" s="3">
-        <v>2914700</v>
+        <v>3468700</v>
       </c>
       <c r="I61" s="3">
-        <v>2879800</v>
+        <v>2986700</v>
       </c>
       <c r="J61" s="3">
+        <v>2950900</v>
+      </c>
+      <c r="K61" s="3">
         <v>1761200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2150700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2413300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2598600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2483700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2640000</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>3479300</v>
+        <v>3462800</v>
       </c>
       <c r="E62" s="3">
-        <v>3988600</v>
+        <v>3565100</v>
       </c>
       <c r="F62" s="3">
-        <v>4032800</v>
+        <v>4087000</v>
       </c>
       <c r="G62" s="3">
-        <v>3950000</v>
+        <v>4132300</v>
       </c>
       <c r="H62" s="3">
-        <v>3701900</v>
+        <v>4047400</v>
       </c>
       <c r="I62" s="3">
-        <v>3048100</v>
+        <v>3793300</v>
       </c>
       <c r="J62" s="3">
+        <v>3123300</v>
+      </c>
+      <c r="K62" s="3">
         <v>2779400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2568500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2821400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1667000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1580900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1679400</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>20274100</v>
+        <v>19191600</v>
       </c>
       <c r="E66" s="3">
-        <v>18585500</v>
+        <v>20774500</v>
       </c>
       <c r="F66" s="3">
-        <v>17454100</v>
+        <v>19044200</v>
       </c>
       <c r="G66" s="3">
-        <v>18300900</v>
+        <v>17884800</v>
       </c>
       <c r="H66" s="3">
-        <v>17164000</v>
+        <v>18752500</v>
       </c>
       <c r="I66" s="3">
-        <v>15385500</v>
+        <v>17587500</v>
       </c>
       <c r="J66" s="3">
+        <v>15765100</v>
+      </c>
+      <c r="K66" s="3">
         <v>14122200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13034000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>16474400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>15189400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14354100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>15579900</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>8045500</v>
+        <v>4882100</v>
       </c>
       <c r="E72" s="3">
-        <v>6318400</v>
+        <v>8244100</v>
       </c>
       <c r="F72" s="3">
-        <v>4528400</v>
+        <v>6474300</v>
       </c>
       <c r="G72" s="3">
-        <v>3669500</v>
+        <v>4640100</v>
       </c>
       <c r="H72" s="3">
-        <v>4303200</v>
+        <v>3760100</v>
       </c>
       <c r="I72" s="3">
-        <v>5243300</v>
+        <v>4409400</v>
       </c>
       <c r="J72" s="3">
+        <v>5372700</v>
+      </c>
+      <c r="K72" s="3">
         <v>8799400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9954100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>11374500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>11652000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>9938400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>11579800</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>12729100</v>
+        <v>9546600</v>
       </c>
       <c r="E76" s="3">
-        <v>10270500</v>
+        <v>13043300</v>
       </c>
       <c r="F76" s="3">
-        <v>8183800</v>
+        <v>10524000</v>
       </c>
       <c r="G76" s="3">
-        <v>7795200</v>
+        <v>8385700</v>
       </c>
       <c r="H76" s="3">
-        <v>8212500</v>
+        <v>7987600</v>
       </c>
       <c r="I76" s="3">
-        <v>9152600</v>
+        <v>8415100</v>
       </c>
       <c r="J76" s="3">
+        <v>9378500</v>
+      </c>
+      <c r="K76" s="3">
         <v>12707200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13855400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>15928500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>16510400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>14226300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>16245300</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>1767900</v>
+        <v>-2558700</v>
       </c>
       <c r="E81" s="3">
-        <v>2142800</v>
+        <v>1811500</v>
       </c>
       <c r="F81" s="3">
-        <v>1650700</v>
+        <v>2195600</v>
       </c>
       <c r="G81" s="3">
-        <v>209900</v>
+        <v>1691500</v>
       </c>
       <c r="H81" s="3">
-        <v>-616600</v>
+        <v>215100</v>
       </c>
       <c r="I81" s="3">
-        <v>-3075800</v>
+        <v>-631800</v>
       </c>
       <c r="J81" s="3">
+        <v>-3151700</v>
+      </c>
+      <c r="K81" s="3">
         <v>78700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1281200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1276900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1413700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>600200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1384300</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>989700</v>
+        <v>1158400</v>
       </c>
       <c r="E83" s="3">
-        <v>817300</v>
+        <v>1014100</v>
       </c>
       <c r="F83" s="3">
-        <v>806100</v>
+        <v>837500</v>
       </c>
       <c r="G83" s="3">
-        <v>811900</v>
+        <v>826000</v>
       </c>
       <c r="H83" s="3">
-        <v>681800</v>
+        <v>832000</v>
       </c>
       <c r="I83" s="3">
-        <v>797900</v>
+        <v>698600</v>
       </c>
       <c r="J83" s="3">
+        <v>817600</v>
+      </c>
+      <c r="K83" s="3">
         <v>839000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>966700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1095700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1195900</v>
       </c>
-      <c r="N83" s="3" t="s">
+      <c r="O83" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1025800</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>2914100</v>
+        <v>694400</v>
       </c>
       <c r="E89" s="3">
-        <v>3688500</v>
+        <v>2986000</v>
       </c>
       <c r="F89" s="3">
-        <v>2731900</v>
+        <v>3779500</v>
       </c>
       <c r="G89" s="3">
-        <v>1593100</v>
+        <v>2799300</v>
       </c>
       <c r="H89" s="3">
-        <v>882100</v>
+        <v>1632500</v>
       </c>
       <c r="I89" s="3">
-        <v>906500</v>
+        <v>903800</v>
       </c>
       <c r="J89" s="3">
+        <v>928900</v>
+      </c>
+      <c r="K89" s="3">
         <v>1322800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1947700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2064300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2047700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2289700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1133200</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
-        <v>-422700</v>
+        <v>-319000</v>
       </c>
       <c r="E91" s="3">
-        <v>-345900</v>
+        <v>-433100</v>
       </c>
       <c r="F91" s="3">
-        <v>-424200</v>
+        <v>-354400</v>
       </c>
       <c r="G91" s="3">
-        <v>-483200</v>
+        <v>-434700</v>
       </c>
       <c r="H91" s="3">
-        <v>-375300</v>
+        <v>-495200</v>
       </c>
       <c r="I91" s="3">
-        <v>-366100</v>
+        <v>-384600</v>
       </c>
       <c r="J91" s="3">
+        <v>-375100</v>
+      </c>
+      <c r="K91" s="3">
         <v>-578700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-788400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-587400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-530300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-564200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-566900</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
-        <v>-3247800</v>
+        <v>-843000</v>
       </c>
       <c r="E94" s="3">
-        <v>-1877400</v>
+        <v>-3327900</v>
       </c>
       <c r="F94" s="3">
-        <v>-1435300</v>
+        <v>-1923700</v>
       </c>
       <c r="G94" s="3">
-        <v>-334300</v>
+        <v>-1470700</v>
       </c>
       <c r="H94" s="3">
-        <v>-390100</v>
+        <v>-342600</v>
       </c>
       <c r="I94" s="3">
-        <v>-1517300</v>
+        <v>-399800</v>
       </c>
       <c r="J94" s="3">
+        <v>-1554800</v>
+      </c>
+      <c r="K94" s="3">
         <v>-782100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-755300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-829300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1308200</v>
       </c>
-      <c r="N94" s="3" t="s">
+      <c r="O94" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>515500</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -3988,50 +4220,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>-786000</v>
+        <v>-869900</v>
       </c>
       <c r="E96" s="3">
-        <v>-628600</v>
+        <v>-805400</v>
       </c>
       <c r="F96" s="3">
-        <v>-470700</v>
+        <v>-644200</v>
       </c>
       <c r="G96" s="3">
-        <v>-311700</v>
+        <v>-482300</v>
       </c>
       <c r="H96" s="3">
-        <v>-323400</v>
+        <v>-319400</v>
       </c>
       <c r="I96" s="3">
-        <v>-323300</v>
+        <v>-331400</v>
       </c>
       <c r="J96" s="3">
+        <v>-331300</v>
+      </c>
+      <c r="K96" s="3">
         <v>-1157900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-1072000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1086800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1077900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-897100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-846300</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>-1504100</v>
+        <v>97400</v>
       </c>
       <c r="E100" s="3">
-        <v>-878800</v>
+        <v>-1541200</v>
       </c>
       <c r="F100" s="3">
-        <v>-1179500</v>
+        <v>-900500</v>
       </c>
       <c r="G100" s="3">
-        <v>-651500</v>
+        <v>-1208600</v>
       </c>
       <c r="H100" s="3">
-        <v>-385000</v>
+        <v>-667600</v>
       </c>
       <c r="I100" s="3">
-        <v>517200</v>
+        <v>-394400</v>
       </c>
       <c r="J100" s="3">
+        <v>530000</v>
+      </c>
+      <c r="K100" s="3">
         <v>-1108700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1012700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2011700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1119700</v>
       </c>
-      <c r="N100" s="3" t="s">
+      <c r="O100" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-737200</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>355300</v>
+        <v>-254500</v>
       </c>
       <c r="E101" s="3">
-        <v>53200</v>
+        <v>364100</v>
       </c>
       <c r="F101" s="3">
-        <v>-255600</v>
+        <v>54500</v>
       </c>
       <c r="G101" s="3">
-        <v>24400</v>
+        <v>-261900</v>
       </c>
       <c r="H101" s="3">
-        <v>129500</v>
+        <v>25000</v>
       </c>
       <c r="I101" s="3">
-        <v>-8600</v>
+        <v>132700</v>
       </c>
       <c r="J101" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="K101" s="3">
         <v>260300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-251900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>654400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>75500</v>
       </c>
-      <c r="N101" s="3" t="s">
+      <c r="O101" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-24600</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>-1482500</v>
+        <v>-305600</v>
       </c>
       <c r="E102" s="3">
-        <v>985600</v>
+        <v>-1519100</v>
       </c>
       <c r="F102" s="3">
-        <v>-138500</v>
+        <v>1009900</v>
       </c>
       <c r="G102" s="3">
-        <v>631700</v>
+        <v>-141900</v>
       </c>
       <c r="H102" s="3">
-        <v>236500</v>
+        <v>647300</v>
       </c>
       <c r="I102" s="3">
-        <v>-102200</v>
+        <v>242400</v>
       </c>
       <c r="J102" s="3">
+        <v>-104700</v>
+      </c>
+      <c r="K102" s="3">
         <v>-307600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-72200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-122200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-304600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>624200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>886800</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/ERIC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ERIC_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>25479200</v>
+        <v>25416000</v>
       </c>
       <c r="E8" s="3">
-        <v>26272100</v>
+        <v>26206900</v>
       </c>
       <c r="F8" s="3">
-        <v>22476400</v>
+        <v>22420600</v>
       </c>
       <c r="G8" s="3">
-        <v>22483700</v>
+        <v>22428000</v>
       </c>
       <c r="H8" s="3">
-        <v>21983100</v>
+        <v>21928600</v>
       </c>
       <c r="I8" s="3">
-        <v>20398600</v>
+        <v>20348000</v>
       </c>
       <c r="J8" s="3">
-        <v>19870300</v>
+        <v>19821000</v>
       </c>
       <c r="K8" s="3">
         <v>20802200</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>15378100</v>
+        <v>15340000</v>
       </c>
       <c r="E9" s="3">
-        <v>15291900</v>
+        <v>15254000</v>
       </c>
       <c r="F9" s="3">
-        <v>12702500</v>
+        <v>12671000</v>
       </c>
       <c r="G9" s="3">
-        <v>13345800</v>
+        <v>13312700</v>
       </c>
       <c r="H9" s="3">
-        <v>13743800</v>
+        <v>13709700</v>
       </c>
       <c r="I9" s="3">
-        <v>13225700</v>
+        <v>13192900</v>
       </c>
       <c r="J9" s="3">
-        <v>14726200</v>
+        <v>14689700</v>
       </c>
       <c r="K9" s="3">
         <v>14312800</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>10101100</v>
+        <v>10076000</v>
       </c>
       <c r="E10" s="3">
-        <v>10980200</v>
+        <v>10952900</v>
       </c>
       <c r="F10" s="3">
-        <v>9773900</v>
+        <v>9749600</v>
       </c>
       <c r="G10" s="3">
-        <v>9137900</v>
+        <v>9115300</v>
       </c>
       <c r="H10" s="3">
-        <v>8239300</v>
+        <v>8218900</v>
       </c>
       <c r="I10" s="3">
-        <v>7172900</v>
+        <v>7155100</v>
       </c>
       <c r="J10" s="3">
-        <v>5144100</v>
+        <v>5131300</v>
       </c>
       <c r="K10" s="3">
         <v>6489400</v>
@@ -880,25 +880,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>4666500</v>
+        <v>4655000</v>
       </c>
       <c r="E12" s="3">
-        <v>4570900</v>
+        <v>4559500</v>
       </c>
       <c r="F12" s="3">
-        <v>4057400</v>
+        <v>4047300</v>
       </c>
       <c r="G12" s="3">
-        <v>3802600</v>
+        <v>3793100</v>
       </c>
       <c r="H12" s="3">
-        <v>3722100</v>
+        <v>3712800</v>
       </c>
       <c r="I12" s="3">
-        <v>3639300</v>
+        <v>3630300</v>
       </c>
       <c r="J12" s="3">
-        <v>3442400</v>
+        <v>3433800</v>
       </c>
       <c r="K12" s="3">
         <v>2728000</v>
@@ -970,25 +970,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>3716900</v>
+        <v>3707700</v>
       </c>
       <c r="E14" s="3">
-        <v>295600</v>
+        <v>294800</v>
       </c>
       <c r="F14" s="3">
-        <v>67000</v>
+        <v>66800</v>
       </c>
       <c r="G14" s="3">
-        <v>139700</v>
+        <v>139400</v>
       </c>
       <c r="H14" s="3">
-        <v>172700</v>
+        <v>172300</v>
       </c>
       <c r="I14" s="3">
-        <v>818300</v>
+        <v>816300</v>
       </c>
       <c r="J14" s="3">
-        <v>2512400</v>
+        <v>2506200</v>
       </c>
       <c r="K14" s="3">
         <v>706600</v>
@@ -1076,25 +1076,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>27445700</v>
+        <v>27377700</v>
       </c>
       <c r="E17" s="3">
-        <v>23657900</v>
+        <v>23599200</v>
       </c>
       <c r="F17" s="3">
-        <v>19401700</v>
+        <v>19353500</v>
       </c>
       <c r="G17" s="3">
-        <v>19793300</v>
+        <v>19744200</v>
       </c>
       <c r="H17" s="3">
-        <v>20961100</v>
+        <v>20909100</v>
       </c>
       <c r="I17" s="3">
-        <v>20278400</v>
+        <v>20228100</v>
       </c>
       <c r="J17" s="3">
-        <v>23231700</v>
+        <v>23174100</v>
       </c>
       <c r="K17" s="3">
         <v>20312500</v>
@@ -1121,25 +1121,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-1966500</v>
+        <v>-1961700</v>
       </c>
       <c r="E18" s="3">
-        <v>2614200</v>
+        <v>2607700</v>
       </c>
       <c r="F18" s="3">
-        <v>3074700</v>
+        <v>3067100</v>
       </c>
       <c r="G18" s="3">
-        <v>2690400</v>
+        <v>2683800</v>
       </c>
       <c r="H18" s="3">
-        <v>1022100</v>
+        <v>1019500</v>
       </c>
       <c r="I18" s="3">
-        <v>120200</v>
+        <v>119900</v>
       </c>
       <c r="J18" s="3">
-        <v>-3361400</v>
+        <v>-3353000</v>
       </c>
       <c r="K18" s="3">
         <v>489800</v>
@@ -1185,25 +1185,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-23900</v>
+        <v>-23800</v>
       </c>
       <c r="E20" s="3">
-        <v>-94300</v>
+        <v>-94100</v>
       </c>
       <c r="F20" s="3">
-        <v>-152800</v>
+        <v>-152400</v>
       </c>
       <c r="G20" s="3">
-        <v>74200</v>
+        <v>74000</v>
       </c>
       <c r="H20" s="3">
         <v>13600</v>
       </c>
       <c r="I20" s="3">
-        <v>-165200</v>
+        <v>-164800</v>
       </c>
       <c r="J20" s="3">
-        <v>-18200</v>
+        <v>-18100</v>
       </c>
       <c r="K20" s="3">
         <v>-88600</v>
@@ -1230,25 +1230,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-819600</v>
+        <v>-842700</v>
       </c>
       <c r="E21" s="3">
-        <v>3544900</v>
+        <v>3514100</v>
       </c>
       <c r="F21" s="3">
-        <v>3768400</v>
+        <v>3740900</v>
       </c>
       <c r="G21" s="3">
-        <v>3599500</v>
+        <v>3572600</v>
       </c>
       <c r="H21" s="3">
-        <v>1876600</v>
+        <v>1853900</v>
       </c>
       <c r="I21" s="3">
-        <v>661100</v>
+        <v>644300</v>
       </c>
       <c r="J21" s="3">
-        <v>-2553200</v>
+        <v>-2564500</v>
       </c>
       <c r="K21" s="3">
         <v>1243700</v>
@@ -1275,25 +1275,25 @@
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>265700</v>
+        <v>265000</v>
       </c>
       <c r="E22" s="3">
-        <v>138900</v>
+        <v>138600</v>
       </c>
       <c r="F22" s="3">
-        <v>92000</v>
+        <v>91800</v>
       </c>
       <c r="G22" s="3">
-        <v>131900</v>
+        <v>131500</v>
       </c>
       <c r="H22" s="3">
-        <v>188000</v>
+        <v>187500</v>
       </c>
       <c r="I22" s="3">
-        <v>96500</v>
+        <v>96200</v>
       </c>
       <c r="J22" s="3">
-        <v>99400</v>
+        <v>99100</v>
       </c>
       <c r="K22" s="3">
         <v>127900</v>
@@ -1320,25 +1320,25 @@
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>-2256100</v>
+        <v>-2250500</v>
       </c>
       <c r="E23" s="3">
-        <v>2380900</v>
+        <v>2375000</v>
       </c>
       <c r="F23" s="3">
-        <v>2829900</v>
+        <v>2822900</v>
       </c>
       <c r="G23" s="3">
-        <v>2632800</v>
+        <v>2626200</v>
       </c>
       <c r="H23" s="3">
-        <v>847700</v>
+        <v>845600</v>
       </c>
       <c r="I23" s="3">
-        <v>-141500</v>
+        <v>-141200</v>
       </c>
       <c r="J23" s="3">
-        <v>-3478900</v>
+        <v>-3470300</v>
       </c>
       <c r="K23" s="3">
         <v>273300</v>
@@ -1365,25 +1365,25 @@
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>269400</v>
+        <v>268800</v>
       </c>
       <c r="E24" s="3">
-        <v>531800</v>
+        <v>530500</v>
       </c>
       <c r="F24" s="3">
-        <v>606600</v>
+        <v>605100</v>
       </c>
       <c r="G24" s="3">
-        <v>927700</v>
+        <v>925400</v>
       </c>
       <c r="H24" s="3">
-        <v>669700</v>
+        <v>668000</v>
       </c>
       <c r="I24" s="3">
-        <v>465700</v>
+        <v>464500</v>
       </c>
       <c r="J24" s="3">
-        <v>-341000</v>
+        <v>-340200</v>
       </c>
       <c r="K24" s="3">
         <v>177700</v>
@@ -1455,25 +1455,25 @@
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>-2525600</v>
+        <v>-2519300</v>
       </c>
       <c r="E26" s="3">
-        <v>1849100</v>
+        <v>1844500</v>
       </c>
       <c r="F26" s="3">
-        <v>2223300</v>
+        <v>2217800</v>
       </c>
       <c r="G26" s="3">
-        <v>1705000</v>
+        <v>1700800</v>
       </c>
       <c r="H26" s="3">
-        <v>178000</v>
+        <v>177600</v>
       </c>
       <c r="I26" s="3">
-        <v>-607200</v>
+        <v>-605700</v>
       </c>
       <c r="J26" s="3">
-        <v>-3137900</v>
+        <v>-3130100</v>
       </c>
       <c r="K26" s="3">
         <v>95600</v>
@@ -1500,25 +1500,25 @@
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>-2558700</v>
+        <v>-2552300</v>
       </c>
       <c r="E27" s="3">
-        <v>1811500</v>
+        <v>1807100</v>
       </c>
       <c r="F27" s="3">
-        <v>2195600</v>
+        <v>2190200</v>
       </c>
       <c r="G27" s="3">
-        <v>1691500</v>
+        <v>1687300</v>
       </c>
       <c r="H27" s="3">
-        <v>215100</v>
+        <v>214500</v>
       </c>
       <c r="I27" s="3">
-        <v>-631800</v>
+        <v>-630200</v>
       </c>
       <c r="J27" s="3">
-        <v>-3151700</v>
+        <v>-3143900</v>
       </c>
       <c r="K27" s="3">
         <v>78700</v>
@@ -1725,25 +1725,25 @@
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>23900</v>
+        <v>23800</v>
       </c>
       <c r="E32" s="3">
-        <v>94300</v>
+        <v>94100</v>
       </c>
       <c r="F32" s="3">
-        <v>152800</v>
+        <v>152400</v>
       </c>
       <c r="G32" s="3">
-        <v>-74200</v>
+        <v>-74000</v>
       </c>
       <c r="H32" s="3">
         <v>-13600</v>
       </c>
       <c r="I32" s="3">
-        <v>165200</v>
+        <v>164800</v>
       </c>
       <c r="J32" s="3">
-        <v>18200</v>
+        <v>18100</v>
       </c>
       <c r="K32" s="3">
         <v>88600</v>
@@ -1770,25 +1770,25 @@
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>-2558700</v>
+        <v>-2552300</v>
       </c>
       <c r="E33" s="3">
-        <v>1811500</v>
+        <v>1807100</v>
       </c>
       <c r="F33" s="3">
-        <v>2195600</v>
+        <v>2190200</v>
       </c>
       <c r="G33" s="3">
-        <v>1691500</v>
+        <v>1687300</v>
       </c>
       <c r="H33" s="3">
-        <v>215100</v>
+        <v>214500</v>
       </c>
       <c r="I33" s="3">
-        <v>-631800</v>
+        <v>-630200</v>
       </c>
       <c r="J33" s="3">
-        <v>-3151700</v>
+        <v>-3143900</v>
       </c>
       <c r="K33" s="3">
         <v>78700</v>
@@ -1860,25 +1860,25 @@
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>-2558700</v>
+        <v>-2552300</v>
       </c>
       <c r="E35" s="3">
-        <v>1811500</v>
+        <v>1807100</v>
       </c>
       <c r="F35" s="3">
-        <v>2195600</v>
+        <v>2190200</v>
       </c>
       <c r="G35" s="3">
-        <v>1691500</v>
+        <v>1687300</v>
       </c>
       <c r="H35" s="3">
-        <v>215100</v>
+        <v>214500</v>
       </c>
       <c r="I35" s="3">
-        <v>-631800</v>
+        <v>-630200</v>
       </c>
       <c r="J35" s="3">
-        <v>-3151700</v>
+        <v>-3143900</v>
       </c>
       <c r="K35" s="3">
         <v>78700</v>
@@ -1993,25 +1993,25 @@
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>3404600</v>
+        <v>3396200</v>
       </c>
       <c r="E41" s="3">
-        <v>3710300</v>
+        <v>3701100</v>
       </c>
       <c r="F41" s="3">
-        <v>5229300</v>
+        <v>5216400</v>
       </c>
       <c r="G41" s="3">
-        <v>4219500</v>
+        <v>4209000</v>
       </c>
       <c r="H41" s="3">
-        <v>4361400</v>
+        <v>4350600</v>
       </c>
       <c r="I41" s="3">
-        <v>3714100</v>
+        <v>3704900</v>
       </c>
       <c r="J41" s="3">
-        <v>3471800</v>
+        <v>3463200</v>
       </c>
       <c r="K41" s="3">
         <v>6980700</v>
@@ -2038,25 +2038,25 @@
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>927300</v>
+        <v>925000</v>
       </c>
       <c r="E42" s="3">
-        <v>845200</v>
+        <v>843100</v>
       </c>
       <c r="F42" s="3">
-        <v>1251200</v>
+        <v>1248100</v>
       </c>
       <c r="G42" s="3">
-        <v>659800</v>
+        <v>658200</v>
       </c>
       <c r="H42" s="3">
-        <v>653900</v>
+        <v>652300</v>
       </c>
       <c r="I42" s="3">
-        <v>641000</v>
+        <v>639400</v>
       </c>
       <c r="J42" s="3">
-        <v>649500</v>
+        <v>647900</v>
       </c>
       <c r="K42" s="3">
         <v>1258100</v>
@@ -2083,25 +2083,25 @@
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>6734800</v>
+        <v>6718100</v>
       </c>
       <c r="E43" s="3">
-        <v>7427700</v>
+        <v>7409300</v>
       </c>
       <c r="F43" s="3">
-        <v>6736300</v>
+        <v>6719600</v>
       </c>
       <c r="G43" s="3">
-        <v>6523900</v>
+        <v>6507800</v>
       </c>
       <c r="H43" s="3">
-        <v>6699100</v>
+        <v>6682400</v>
       </c>
       <c r="I43" s="3">
-        <v>8139100</v>
+        <v>8118900</v>
       </c>
       <c r="J43" s="3">
-        <v>14100300</v>
+        <v>14065400</v>
       </c>
       <c r="K43" s="3">
         <v>16876900</v>
@@ -2128,25 +2128,25 @@
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>3490100</v>
+        <v>3481400</v>
       </c>
       <c r="E44" s="3">
-        <v>4435600</v>
+        <v>4424600</v>
       </c>
       <c r="F44" s="3">
-        <v>3402100</v>
+        <v>3393700</v>
       </c>
       <c r="G44" s="3">
-        <v>2718400</v>
+        <v>2711600</v>
       </c>
       <c r="H44" s="3">
-        <v>2986000</v>
+        <v>2978600</v>
       </c>
       <c r="I44" s="3">
-        <v>2830400</v>
+        <v>2823400</v>
       </c>
       <c r="J44" s="3">
-        <v>2471700</v>
+        <v>2465500</v>
       </c>
       <c r="K44" s="3">
         <v>5847000</v>
@@ -2173,25 +2173,25 @@
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>438400</v>
+        <v>437300</v>
       </c>
       <c r="E45" s="3">
-        <v>396700</v>
+        <v>395700</v>
       </c>
       <c r="F45" s="3">
-        <v>293400</v>
+        <v>292700</v>
       </c>
       <c r="G45" s="3">
-        <v>371000</v>
+        <v>370100</v>
       </c>
       <c r="H45" s="3">
-        <v>190800</v>
+        <v>190300</v>
       </c>
       <c r="I45" s="3">
-        <v>268300</v>
+        <v>267600</v>
       </c>
       <c r="J45" s="3">
-        <v>395800</v>
+        <v>394800</v>
       </c>
       <c r="K45" s="3">
         <v>660300</v>
@@ -2218,25 +2218,25 @@
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>14995100</v>
+        <v>14957900</v>
       </c>
       <c r="E46" s="3">
-        <v>16815400</v>
+        <v>16773700</v>
       </c>
       <c r="F46" s="3">
-        <v>16912400</v>
+        <v>16870400</v>
       </c>
       <c r="G46" s="3">
-        <v>14492700</v>
+        <v>14456700</v>
       </c>
       <c r="H46" s="3">
-        <v>14891200</v>
+        <v>14854200</v>
       </c>
       <c r="I46" s="3">
-        <v>15592900</v>
+        <v>15554200</v>
       </c>
       <c r="J46" s="3">
-        <v>14843700</v>
+        <v>14806900</v>
       </c>
       <c r="K46" s="3">
         <v>16532700</v>
@@ -2263,25 +2263,25 @@
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>2019100</v>
+        <v>2014100</v>
       </c>
       <c r="E47" s="3">
-        <v>1898100</v>
+        <v>1893400</v>
       </c>
       <c r="F47" s="3">
-        <v>3929000</v>
+        <v>3919300</v>
       </c>
       <c r="G47" s="3">
-        <v>2947900</v>
+        <v>2940600</v>
       </c>
       <c r="H47" s="3">
-        <v>3021200</v>
+        <v>3013700</v>
       </c>
       <c r="I47" s="3">
-        <v>3274700</v>
+        <v>3266600</v>
       </c>
       <c r="J47" s="3">
-        <v>3386000</v>
+        <v>3377600</v>
       </c>
       <c r="K47" s="3">
         <v>1940600</v>
@@ -2308,25 +2308,25 @@
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>1791300</v>
+        <v>1786900</v>
       </c>
       <c r="E48" s="3">
-        <v>2138800</v>
+        <v>2133500</v>
       </c>
       <c r="F48" s="3">
-        <v>2082800</v>
+        <v>2077700</v>
       </c>
       <c r="G48" s="3">
-        <v>2066900</v>
+        <v>2061700</v>
       </c>
       <c r="H48" s="3">
-        <v>2161100</v>
+        <v>2155700</v>
       </c>
       <c r="I48" s="3">
-        <v>1243100</v>
+        <v>1240100</v>
       </c>
       <c r="J48" s="3">
-        <v>1243900</v>
+        <v>1240800</v>
       </c>
       <c r="K48" s="3">
         <v>3160000</v>
@@ -2353,25 +2353,25 @@
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>7768000</v>
+        <v>7748700</v>
       </c>
       <c r="E49" s="3">
-        <v>11089000</v>
+        <v>11061500</v>
       </c>
       <c r="F49" s="3">
-        <v>4408100</v>
+        <v>4397200</v>
       </c>
       <c r="G49" s="3">
-        <v>4219000</v>
+        <v>4208500</v>
       </c>
       <c r="H49" s="3">
-        <v>3650500</v>
+        <v>3641400</v>
       </c>
       <c r="I49" s="3">
-        <v>3651900</v>
+        <v>3642900</v>
       </c>
       <c r="J49" s="3">
-        <v>3536800</v>
+        <v>3528000</v>
       </c>
       <c r="K49" s="3">
         <v>11181200</v>
@@ -2488,25 +2488,25 @@
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>2164800</v>
+        <v>2159400</v>
       </c>
       <c r="E52" s="3">
-        <v>1876400</v>
+        <v>1871700</v>
       </c>
       <c r="F52" s="3">
-        <v>2235800</v>
+        <v>2230200</v>
       </c>
       <c r="G52" s="3">
-        <v>2544100</v>
+        <v>2537800</v>
       </c>
       <c r="H52" s="3">
-        <v>3016100</v>
+        <v>3008600</v>
       </c>
       <c r="I52" s="3">
-        <v>2240000</v>
+        <v>2234400</v>
       </c>
       <c r="J52" s="3">
-        <v>2133200</v>
+        <v>2127900</v>
       </c>
       <c r="K52" s="3">
         <v>1605000</v>
@@ -2578,25 +2578,25 @@
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>28738200</v>
+        <v>28666900</v>
       </c>
       <c r="E54" s="3">
-        <v>33817700</v>
+        <v>33733800</v>
       </c>
       <c r="F54" s="3">
-        <v>29568200</v>
+        <v>29494800</v>
       </c>
       <c r="G54" s="3">
-        <v>26270500</v>
+        <v>26205400</v>
       </c>
       <c r="H54" s="3">
-        <v>26740100</v>
+        <v>26673700</v>
       </c>
       <c r="I54" s="3">
-        <v>26002600</v>
+        <v>25938100</v>
       </c>
       <c r="J54" s="3">
-        <v>25143600</v>
+        <v>25081200</v>
       </c>
       <c r="K54" s="3">
         <v>26829400</v>
@@ -2661,25 +2661,25 @@
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>2686600</v>
+        <v>2679900</v>
       </c>
       <c r="E57" s="3">
-        <v>3718800</v>
+        <v>3709600</v>
       </c>
       <c r="F57" s="3">
-        <v>3452400</v>
+        <v>3443900</v>
       </c>
       <c r="G57" s="3">
-        <v>3094800</v>
+        <v>3087200</v>
       </c>
       <c r="H57" s="3">
-        <v>2941500</v>
+        <v>2934200</v>
       </c>
       <c r="I57" s="3">
-        <v>2891200</v>
+        <v>2884000</v>
       </c>
       <c r="J57" s="3">
-        <v>2546500</v>
+        <v>2540100</v>
       </c>
       <c r="K57" s="3">
         <v>4830700</v>
@@ -2706,25 +2706,25 @@
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>1924400</v>
+        <v>1919600</v>
       </c>
       <c r="E58" s="3">
-        <v>819500</v>
+        <v>817400</v>
       </c>
       <c r="F58" s="3">
-        <v>1143000</v>
+        <v>1140200</v>
       </c>
       <c r="G58" s="3">
-        <v>980900</v>
+        <v>978400</v>
       </c>
       <c r="H58" s="3">
-        <v>1134500</v>
+        <v>1131700</v>
       </c>
       <c r="I58" s="3">
-        <v>218200</v>
+        <v>217600</v>
       </c>
       <c r="J58" s="3">
-        <v>246200</v>
+        <v>245600</v>
       </c>
       <c r="K58" s="3">
         <v>1517000</v>
@@ -2751,25 +2751,25 @@
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>7908400</v>
+        <v>7888800</v>
       </c>
       <c r="E59" s="3">
-        <v>9550500</v>
+        <v>9526800</v>
       </c>
       <c r="F59" s="3">
-        <v>7687200</v>
+        <v>7668100</v>
       </c>
       <c r="G59" s="3">
-        <v>6984800</v>
+        <v>6967400</v>
       </c>
       <c r="H59" s="3">
-        <v>7226300</v>
+        <v>7208300</v>
       </c>
       <c r="I59" s="3">
-        <v>7621600</v>
+        <v>7602700</v>
       </c>
       <c r="J59" s="3">
-        <v>9455300</v>
+        <v>9431800</v>
       </c>
       <c r="K59" s="3">
         <v>11607000</v>
@@ -2796,25 +2796,25 @@
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>12519400</v>
+        <v>12488300</v>
       </c>
       <c r="E60" s="3">
-        <v>14088700</v>
+        <v>14053800</v>
       </c>
       <c r="F60" s="3">
-        <v>12282600</v>
+        <v>12252100</v>
       </c>
       <c r="G60" s="3">
-        <v>11060500</v>
+        <v>11033000</v>
       </c>
       <c r="H60" s="3">
-        <v>11302200</v>
+        <v>11274200</v>
       </c>
       <c r="I60" s="3">
-        <v>10730900</v>
+        <v>10704300</v>
       </c>
       <c r="J60" s="3">
-        <v>9629400</v>
+        <v>9605500</v>
       </c>
       <c r="K60" s="3">
         <v>9517800</v>
@@ -2841,25 +2841,25 @@
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>3331900</v>
+        <v>3323600</v>
       </c>
       <c r="E61" s="3">
-        <v>3266700</v>
+        <v>3258600</v>
       </c>
       <c r="F61" s="3">
-        <v>2836700</v>
+        <v>2829700</v>
       </c>
       <c r="G61" s="3">
-        <v>2836900</v>
+        <v>2829900</v>
       </c>
       <c r="H61" s="3">
-        <v>3468700</v>
+        <v>3460100</v>
       </c>
       <c r="I61" s="3">
-        <v>2986700</v>
+        <v>2979300</v>
       </c>
       <c r="J61" s="3">
-        <v>2950900</v>
+        <v>2943600</v>
       </c>
       <c r="K61" s="3">
         <v>1761200</v>
@@ -2886,25 +2886,25 @@
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>3462800</v>
+        <v>3454200</v>
       </c>
       <c r="E62" s="3">
-        <v>3565100</v>
+        <v>3556300</v>
       </c>
       <c r="F62" s="3">
-        <v>4087000</v>
+        <v>4076900</v>
       </c>
       <c r="G62" s="3">
-        <v>4132300</v>
+        <v>4122000</v>
       </c>
       <c r="H62" s="3">
-        <v>4047400</v>
+        <v>4037400</v>
       </c>
       <c r="I62" s="3">
-        <v>3793300</v>
+        <v>3783900</v>
       </c>
       <c r="J62" s="3">
-        <v>3123300</v>
+        <v>3115500</v>
       </c>
       <c r="K62" s="3">
         <v>2779400</v>
@@ -3066,25 +3066,25 @@
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>19191600</v>
+        <v>19144000</v>
       </c>
       <c r="E66" s="3">
-        <v>20774500</v>
+        <v>20722900</v>
       </c>
       <c r="F66" s="3">
-        <v>19044200</v>
+        <v>18996900</v>
       </c>
       <c r="G66" s="3">
-        <v>17884800</v>
+        <v>17840500</v>
       </c>
       <c r="H66" s="3">
-        <v>18752500</v>
+        <v>18706000</v>
       </c>
       <c r="I66" s="3">
-        <v>17587500</v>
+        <v>17543900</v>
       </c>
       <c r="J66" s="3">
-        <v>15765100</v>
+        <v>15726000</v>
       </c>
       <c r="K66" s="3">
         <v>14122200</v>
@@ -3310,25 +3310,25 @@
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>4882100</v>
+        <v>4870000</v>
       </c>
       <c r="E72" s="3">
-        <v>8244100</v>
+        <v>8223600</v>
       </c>
       <c r="F72" s="3">
-        <v>6474300</v>
+        <v>6458300</v>
       </c>
       <c r="G72" s="3">
-        <v>4640100</v>
+        <v>4628600</v>
       </c>
       <c r="H72" s="3">
-        <v>3760100</v>
+        <v>3750800</v>
       </c>
       <c r="I72" s="3">
-        <v>4409400</v>
+        <v>4398400</v>
       </c>
       <c r="J72" s="3">
-        <v>5372700</v>
+        <v>5359400</v>
       </c>
       <c r="K72" s="3">
         <v>8799400</v>
@@ -3490,25 +3490,25 @@
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>9546600</v>
+        <v>9522900</v>
       </c>
       <c r="E76" s="3">
-        <v>13043300</v>
+        <v>13010900</v>
       </c>
       <c r="F76" s="3">
-        <v>10524000</v>
+        <v>10497900</v>
       </c>
       <c r="G76" s="3">
-        <v>8385700</v>
+        <v>8364900</v>
       </c>
       <c r="H76" s="3">
-        <v>7987600</v>
+        <v>7967800</v>
       </c>
       <c r="I76" s="3">
-        <v>8415100</v>
+        <v>8394200</v>
       </c>
       <c r="J76" s="3">
-        <v>9378500</v>
+        <v>9355200</v>
       </c>
       <c r="K76" s="3">
         <v>12707200</v>
@@ -3630,25 +3630,25 @@
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>-2558700</v>
+        <v>-2552300</v>
       </c>
       <c r="E81" s="3">
-        <v>1811500</v>
+        <v>1807100</v>
       </c>
       <c r="F81" s="3">
-        <v>2195600</v>
+        <v>2190200</v>
       </c>
       <c r="G81" s="3">
-        <v>1691500</v>
+        <v>1687300</v>
       </c>
       <c r="H81" s="3">
-        <v>215100</v>
+        <v>214500</v>
       </c>
       <c r="I81" s="3">
-        <v>-631800</v>
+        <v>-630200</v>
       </c>
       <c r="J81" s="3">
-        <v>-3151700</v>
+        <v>-3143900</v>
       </c>
       <c r="K81" s="3">
         <v>78700</v>
@@ -3694,25 +3694,25 @@
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>1158400</v>
+        <v>1155500</v>
       </c>
       <c r="E83" s="3">
-        <v>1014100</v>
+        <v>1011600</v>
       </c>
       <c r="F83" s="3">
-        <v>837500</v>
+        <v>835400</v>
       </c>
       <c r="G83" s="3">
-        <v>826000</v>
+        <v>823900</v>
       </c>
       <c r="H83" s="3">
-        <v>832000</v>
+        <v>829900</v>
       </c>
       <c r="I83" s="3">
-        <v>698600</v>
+        <v>696900</v>
       </c>
       <c r="J83" s="3">
-        <v>817600</v>
+        <v>815600</v>
       </c>
       <c r="K83" s="3">
         <v>839000</v>
@@ -3964,25 +3964,25 @@
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>694400</v>
+        <v>692700</v>
       </c>
       <c r="E89" s="3">
-        <v>2986000</v>
+        <v>2978600</v>
       </c>
       <c r="F89" s="3">
-        <v>3779500</v>
+        <v>3770200</v>
       </c>
       <c r="G89" s="3">
-        <v>2799300</v>
+        <v>2792300</v>
       </c>
       <c r="H89" s="3">
-        <v>1632500</v>
+        <v>1628400</v>
       </c>
       <c r="I89" s="3">
-        <v>903800</v>
+        <v>901600</v>
       </c>
       <c r="J89" s="3">
-        <v>928900</v>
+        <v>926600</v>
       </c>
       <c r="K89" s="3">
         <v>1322800</v>
@@ -4028,25 +4028,25 @@
         <v>79</v>
       </c>
       <c r="D91" s="3">
-        <v>-319000</v>
+        <v>-318200</v>
       </c>
       <c r="E91" s="3">
-        <v>-433100</v>
+        <v>-432100</v>
       </c>
       <c r="F91" s="3">
-        <v>-354400</v>
+        <v>-353500</v>
       </c>
       <c r="G91" s="3">
-        <v>-434700</v>
+        <v>-433600</v>
       </c>
       <c r="H91" s="3">
-        <v>-495200</v>
+        <v>-493900</v>
       </c>
       <c r="I91" s="3">
-        <v>-384600</v>
+        <v>-383600</v>
       </c>
       <c r="J91" s="3">
-        <v>-375100</v>
+        <v>-374200</v>
       </c>
       <c r="K91" s="3">
         <v>-578700</v>
@@ -4163,25 +4163,25 @@
         <v>82</v>
       </c>
       <c r="D94" s="3">
-        <v>-843000</v>
+        <v>-840900</v>
       </c>
       <c r="E94" s="3">
-        <v>-3327900</v>
+        <v>-3319700</v>
       </c>
       <c r="F94" s="3">
-        <v>-1923700</v>
+        <v>-1918900</v>
       </c>
       <c r="G94" s="3">
-        <v>-1470700</v>
+        <v>-1467000</v>
       </c>
       <c r="H94" s="3">
-        <v>-342600</v>
+        <v>-341700</v>
       </c>
       <c r="I94" s="3">
-        <v>-399800</v>
+        <v>-398800</v>
       </c>
       <c r="J94" s="3">
-        <v>-1554800</v>
+        <v>-1550900</v>
       </c>
       <c r="K94" s="3">
         <v>-782100</v>
@@ -4227,25 +4227,25 @@
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>-869900</v>
+        <v>-867700</v>
       </c>
       <c r="E96" s="3">
-        <v>-805400</v>
+        <v>-803400</v>
       </c>
       <c r="F96" s="3">
-        <v>-644200</v>
+        <v>-642600</v>
       </c>
       <c r="G96" s="3">
-        <v>-482300</v>
+        <v>-481100</v>
       </c>
       <c r="H96" s="3">
-        <v>-319400</v>
+        <v>-318600</v>
       </c>
       <c r="I96" s="3">
-        <v>-331400</v>
+        <v>-330500</v>
       </c>
       <c r="J96" s="3">
-        <v>-331300</v>
+        <v>-330500</v>
       </c>
       <c r="K96" s="3">
         <v>-1157900</v>
@@ -4407,25 +4407,25 @@
         <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>97400</v>
+        <v>97200</v>
       </c>
       <c r="E100" s="3">
-        <v>-1541200</v>
+        <v>-1537400</v>
       </c>
       <c r="F100" s="3">
-        <v>-900500</v>
+        <v>-898200</v>
       </c>
       <c r="G100" s="3">
-        <v>-1208600</v>
+        <v>-1205600</v>
       </c>
       <c r="H100" s="3">
-        <v>-667600</v>
+        <v>-665900</v>
       </c>
       <c r="I100" s="3">
-        <v>-394400</v>
+        <v>-393500</v>
       </c>
       <c r="J100" s="3">
-        <v>530000</v>
+        <v>528700</v>
       </c>
       <c r="K100" s="3">
         <v>-1108700</v>
@@ -4452,22 +4452,22 @@
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>-254500</v>
+        <v>-253800</v>
       </c>
       <c r="E101" s="3">
-        <v>364100</v>
+        <v>363200</v>
       </c>
       <c r="F101" s="3">
-        <v>54500</v>
+        <v>54300</v>
       </c>
       <c r="G101" s="3">
-        <v>-261900</v>
+        <v>-261300</v>
       </c>
       <c r="H101" s="3">
-        <v>25000</v>
+        <v>24900</v>
       </c>
       <c r="I101" s="3">
-        <v>132700</v>
+        <v>132400</v>
       </c>
       <c r="J101" s="3">
         <v>-8800</v>
@@ -4497,25 +4497,25 @@
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>-305600</v>
+        <v>-304900</v>
       </c>
       <c r="E102" s="3">
-        <v>-1519100</v>
+        <v>-1515300</v>
       </c>
       <c r="F102" s="3">
-        <v>1009900</v>
+        <v>1007400</v>
       </c>
       <c r="G102" s="3">
-        <v>-141900</v>
+        <v>-141600</v>
       </c>
       <c r="H102" s="3">
-        <v>647300</v>
+        <v>645700</v>
       </c>
       <c r="I102" s="3">
-        <v>242400</v>
+        <v>241800</v>
       </c>
       <c r="J102" s="3">
-        <v>-104700</v>
+        <v>-104400</v>
       </c>
       <c r="K102" s="3">
         <v>-307600</v>

--- a/AAII_Financials/Yearly/ERIC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ERIC_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>25416000</v>
+        <v>25795200</v>
       </c>
       <c r="E8" s="3">
-        <v>26206900</v>
+        <v>26597900</v>
       </c>
       <c r="F8" s="3">
-        <v>22420600</v>
+        <v>22755200</v>
       </c>
       <c r="G8" s="3">
-        <v>22428000</v>
+        <v>22762600</v>
       </c>
       <c r="H8" s="3">
-        <v>21928600</v>
+        <v>22255800</v>
       </c>
       <c r="I8" s="3">
-        <v>20348000</v>
+        <v>20651600</v>
       </c>
       <c r="J8" s="3">
-        <v>19821000</v>
+        <v>20116800</v>
       </c>
       <c r="K8" s="3">
         <v>20802200</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>15340000</v>
+        <v>15568900</v>
       </c>
       <c r="E9" s="3">
-        <v>15254000</v>
+        <v>15481600</v>
       </c>
       <c r="F9" s="3">
-        <v>12671000</v>
+        <v>12860100</v>
       </c>
       <c r="G9" s="3">
-        <v>13312700</v>
+        <v>13511300</v>
       </c>
       <c r="H9" s="3">
-        <v>13709700</v>
+        <v>13914300</v>
       </c>
       <c r="I9" s="3">
-        <v>13192900</v>
+        <v>13389800</v>
       </c>
       <c r="J9" s="3">
-        <v>14689700</v>
+        <v>14908900</v>
       </c>
       <c r="K9" s="3">
         <v>14312800</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>10076000</v>
+        <v>10226400</v>
       </c>
       <c r="E10" s="3">
-        <v>10952900</v>
+        <v>11116300</v>
       </c>
       <c r="F10" s="3">
-        <v>9749600</v>
+        <v>9895100</v>
       </c>
       <c r="G10" s="3">
-        <v>9115300</v>
+        <v>9251300</v>
       </c>
       <c r="H10" s="3">
-        <v>8218900</v>
+        <v>8341500</v>
       </c>
       <c r="I10" s="3">
-        <v>7155100</v>
+        <v>7261800</v>
       </c>
       <c r="J10" s="3">
-        <v>5131300</v>
+        <v>5207900</v>
       </c>
       <c r="K10" s="3">
         <v>6489400</v>
@@ -880,25 +880,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>4655000</v>
+        <v>4724400</v>
       </c>
       <c r="E12" s="3">
-        <v>4559500</v>
+        <v>4627500</v>
       </c>
       <c r="F12" s="3">
-        <v>4047300</v>
+        <v>4107700</v>
       </c>
       <c r="G12" s="3">
-        <v>3793100</v>
+        <v>3849700</v>
       </c>
       <c r="H12" s="3">
-        <v>3712800</v>
+        <v>3768200</v>
       </c>
       <c r="I12" s="3">
-        <v>3630300</v>
+        <v>3684500</v>
       </c>
       <c r="J12" s="3">
-        <v>3433800</v>
+        <v>3485100</v>
       </c>
       <c r="K12" s="3">
         <v>2728000</v>
@@ -970,25 +970,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>3707700</v>
+        <v>3763000</v>
       </c>
       <c r="E14" s="3">
-        <v>294800</v>
+        <v>397200</v>
       </c>
       <c r="F14" s="3">
-        <v>66800</v>
+        <v>67800</v>
       </c>
       <c r="G14" s="3">
-        <v>139400</v>
+        <v>141400</v>
       </c>
       <c r="H14" s="3">
-        <v>172300</v>
+        <v>174800</v>
       </c>
       <c r="I14" s="3">
-        <v>816300</v>
+        <v>828500</v>
       </c>
       <c r="J14" s="3">
-        <v>2506200</v>
+        <v>2543600</v>
       </c>
       <c r="K14" s="3">
         <v>706600</v>
@@ -1076,25 +1076,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>27377700</v>
+        <v>27786200</v>
       </c>
       <c r="E17" s="3">
-        <v>23599200</v>
+        <v>23951300</v>
       </c>
       <c r="F17" s="3">
-        <v>19353500</v>
+        <v>19642300</v>
       </c>
       <c r="G17" s="3">
-        <v>19744200</v>
+        <v>20038800</v>
       </c>
       <c r="H17" s="3">
-        <v>20909100</v>
+        <v>21221100</v>
       </c>
       <c r="I17" s="3">
-        <v>20228100</v>
+        <v>20529900</v>
       </c>
       <c r="J17" s="3">
-        <v>23174100</v>
+        <v>23519900</v>
       </c>
       <c r="K17" s="3">
         <v>20312500</v>
@@ -1121,25 +1121,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-1961700</v>
+        <v>-1990900</v>
       </c>
       <c r="E18" s="3">
-        <v>2607700</v>
+        <v>2646600</v>
       </c>
       <c r="F18" s="3">
-        <v>3067100</v>
+        <v>3112900</v>
       </c>
       <c r="G18" s="3">
-        <v>2683800</v>
+        <v>2723800</v>
       </c>
       <c r="H18" s="3">
-        <v>1019500</v>
+        <v>1034700</v>
       </c>
       <c r="I18" s="3">
-        <v>119900</v>
+        <v>121700</v>
       </c>
       <c r="J18" s="3">
-        <v>-3353000</v>
+        <v>-3403100</v>
       </c>
       <c r="K18" s="3">
         <v>489800</v>
@@ -1185,25 +1185,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-23800</v>
+        <v>-24200</v>
       </c>
       <c r="E20" s="3">
-        <v>-94100</v>
+        <v>-95500</v>
       </c>
       <c r="F20" s="3">
-        <v>-152400</v>
+        <v>-154700</v>
       </c>
       <c r="G20" s="3">
-        <v>74000</v>
+        <v>75100</v>
       </c>
       <c r="H20" s="3">
-        <v>13600</v>
+        <v>13800</v>
       </c>
       <c r="I20" s="3">
-        <v>-164800</v>
+        <v>-167300</v>
       </c>
       <c r="J20" s="3">
-        <v>-18100</v>
+        <v>-18400</v>
       </c>
       <c r="K20" s="3">
         <v>-88600</v>
@@ -1230,25 +1230,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-842700</v>
+        <v>-850600</v>
       </c>
       <c r="E21" s="3">
-        <v>3514100</v>
+        <v>3570600</v>
       </c>
       <c r="F21" s="3">
-        <v>3740900</v>
+        <v>3800100</v>
       </c>
       <c r="G21" s="3">
-        <v>3572600</v>
+        <v>3629200</v>
       </c>
       <c r="H21" s="3">
-        <v>1853900</v>
+        <v>1884900</v>
       </c>
       <c r="I21" s="3">
-        <v>644300</v>
+        <v>656700</v>
       </c>
       <c r="J21" s="3">
-        <v>-2564500</v>
+        <v>-2599500</v>
       </c>
       <c r="K21" s="3">
         <v>1243700</v>
@@ -1275,25 +1275,25 @@
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>265000</v>
+        <v>269000</v>
       </c>
       <c r="E22" s="3">
-        <v>138600</v>
+        <v>140700</v>
       </c>
       <c r="F22" s="3">
-        <v>91800</v>
+        <v>93200</v>
       </c>
       <c r="G22" s="3">
-        <v>131500</v>
+        <v>133500</v>
       </c>
       <c r="H22" s="3">
-        <v>187500</v>
+        <v>190300</v>
       </c>
       <c r="I22" s="3">
-        <v>96200</v>
+        <v>97700</v>
       </c>
       <c r="J22" s="3">
-        <v>99100</v>
+        <v>100600</v>
       </c>
       <c r="K22" s="3">
         <v>127900</v>
@@ -1320,25 +1320,25 @@
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>-2250500</v>
+        <v>-2284100</v>
       </c>
       <c r="E23" s="3">
-        <v>2375000</v>
+        <v>2410500</v>
       </c>
       <c r="F23" s="3">
-        <v>2822900</v>
+        <v>2865000</v>
       </c>
       <c r="G23" s="3">
-        <v>2626200</v>
+        <v>2665400</v>
       </c>
       <c r="H23" s="3">
-        <v>845600</v>
+        <v>858200</v>
       </c>
       <c r="I23" s="3">
-        <v>-141200</v>
+        <v>-143300</v>
       </c>
       <c r="J23" s="3">
-        <v>-3470300</v>
+        <v>-3522100</v>
       </c>
       <c r="K23" s="3">
         <v>273300</v>
@@ -1365,25 +1365,25 @@
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>268800</v>
+        <v>272800</v>
       </c>
       <c r="E24" s="3">
-        <v>530500</v>
+        <v>538400</v>
       </c>
       <c r="F24" s="3">
-        <v>605100</v>
+        <v>614100</v>
       </c>
       <c r="G24" s="3">
-        <v>925400</v>
+        <v>939200</v>
       </c>
       <c r="H24" s="3">
-        <v>668000</v>
+        <v>678000</v>
       </c>
       <c r="I24" s="3">
-        <v>464500</v>
+        <v>471400</v>
       </c>
       <c r="J24" s="3">
-        <v>-340200</v>
+        <v>-345300</v>
       </c>
       <c r="K24" s="3">
         <v>177700</v>
@@ -1455,25 +1455,25 @@
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>-2519300</v>
+        <v>-2556900</v>
       </c>
       <c r="E26" s="3">
-        <v>1844500</v>
+        <v>1872000</v>
       </c>
       <c r="F26" s="3">
-        <v>2217800</v>
+        <v>2250900</v>
       </c>
       <c r="G26" s="3">
-        <v>1700800</v>
+        <v>1726200</v>
       </c>
       <c r="H26" s="3">
-        <v>177600</v>
+        <v>180200</v>
       </c>
       <c r="I26" s="3">
-        <v>-605700</v>
+        <v>-614700</v>
       </c>
       <c r="J26" s="3">
-        <v>-3130100</v>
+        <v>-3176800</v>
       </c>
       <c r="K26" s="3">
         <v>95600</v>
@@ -1500,25 +1500,25 @@
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>-2552300</v>
+        <v>-2590400</v>
       </c>
       <c r="E27" s="3">
-        <v>1807100</v>
+        <v>1834000</v>
       </c>
       <c r="F27" s="3">
-        <v>2190200</v>
+        <v>2222900</v>
       </c>
       <c r="G27" s="3">
-        <v>1687300</v>
+        <v>1712500</v>
       </c>
       <c r="H27" s="3">
-        <v>214500</v>
+        <v>217700</v>
       </c>
       <c r="I27" s="3">
-        <v>-630200</v>
+        <v>-639600</v>
       </c>
       <c r="J27" s="3">
-        <v>-3143900</v>
+        <v>-3190800</v>
       </c>
       <c r="K27" s="3">
         <v>78700</v>
@@ -1725,25 +1725,25 @@
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>23800</v>
+        <v>24200</v>
       </c>
       <c r="E32" s="3">
-        <v>94100</v>
+        <v>95500</v>
       </c>
       <c r="F32" s="3">
-        <v>152400</v>
+        <v>154700</v>
       </c>
       <c r="G32" s="3">
-        <v>-74000</v>
+        <v>-75100</v>
       </c>
       <c r="H32" s="3">
-        <v>-13600</v>
+        <v>-13800</v>
       </c>
       <c r="I32" s="3">
-        <v>164800</v>
+        <v>167300</v>
       </c>
       <c r="J32" s="3">
-        <v>18100</v>
+        <v>18400</v>
       </c>
       <c r="K32" s="3">
         <v>88600</v>
@@ -1770,25 +1770,25 @@
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>-2552300</v>
+        <v>-2590400</v>
       </c>
       <c r="E33" s="3">
-        <v>1807100</v>
+        <v>1834000</v>
       </c>
       <c r="F33" s="3">
-        <v>2190200</v>
+        <v>2222900</v>
       </c>
       <c r="G33" s="3">
-        <v>1687300</v>
+        <v>1712500</v>
       </c>
       <c r="H33" s="3">
-        <v>214500</v>
+        <v>217700</v>
       </c>
       <c r="I33" s="3">
-        <v>-630200</v>
+        <v>-639600</v>
       </c>
       <c r="J33" s="3">
-        <v>-3143900</v>
+        <v>-3190800</v>
       </c>
       <c r="K33" s="3">
         <v>78700</v>
@@ -1860,25 +1860,25 @@
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>-2552300</v>
+        <v>-2590400</v>
       </c>
       <c r="E35" s="3">
-        <v>1807100</v>
+        <v>1834000</v>
       </c>
       <c r="F35" s="3">
-        <v>2190200</v>
+        <v>2222900</v>
       </c>
       <c r="G35" s="3">
-        <v>1687300</v>
+        <v>1712500</v>
       </c>
       <c r="H35" s="3">
-        <v>214500</v>
+        <v>217700</v>
       </c>
       <c r="I35" s="3">
-        <v>-630200</v>
+        <v>-639600</v>
       </c>
       <c r="J35" s="3">
-        <v>-3143900</v>
+        <v>-3190800</v>
       </c>
       <c r="K35" s="3">
         <v>78700</v>
@@ -1993,25 +1993,25 @@
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>3396200</v>
+        <v>3446900</v>
       </c>
       <c r="E41" s="3">
-        <v>3701100</v>
+        <v>3756300</v>
       </c>
       <c r="F41" s="3">
-        <v>5216400</v>
+        <v>5294200</v>
       </c>
       <c r="G41" s="3">
-        <v>4209000</v>
+        <v>4271800</v>
       </c>
       <c r="H41" s="3">
-        <v>4350600</v>
+        <v>4415500</v>
       </c>
       <c r="I41" s="3">
-        <v>3704900</v>
+        <v>3760200</v>
       </c>
       <c r="J41" s="3">
-        <v>3463200</v>
+        <v>3514800</v>
       </c>
       <c r="K41" s="3">
         <v>6980700</v>
@@ -2038,25 +2038,25 @@
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>925000</v>
+        <v>938800</v>
       </c>
       <c r="E42" s="3">
-        <v>843100</v>
+        <v>855700</v>
       </c>
       <c r="F42" s="3">
-        <v>1248100</v>
+        <v>1266700</v>
       </c>
       <c r="G42" s="3">
-        <v>658200</v>
+        <v>668000</v>
       </c>
       <c r="H42" s="3">
-        <v>652300</v>
+        <v>662000</v>
       </c>
       <c r="I42" s="3">
-        <v>639400</v>
+        <v>648900</v>
       </c>
       <c r="J42" s="3">
-        <v>647900</v>
+        <v>657500</v>
       </c>
       <c r="K42" s="3">
         <v>1258100</v>
@@ -2083,25 +2083,25 @@
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>6718100</v>
+        <v>6818300</v>
       </c>
       <c r="E43" s="3">
-        <v>7409300</v>
+        <v>7519800</v>
       </c>
       <c r="F43" s="3">
-        <v>6719600</v>
+        <v>6819900</v>
       </c>
       <c r="G43" s="3">
-        <v>6507800</v>
+        <v>6604900</v>
       </c>
       <c r="H43" s="3">
-        <v>6682400</v>
+        <v>6782200</v>
       </c>
       <c r="I43" s="3">
-        <v>8118900</v>
+        <v>8240000</v>
       </c>
       <c r="J43" s="3">
-        <v>14065400</v>
+        <v>14275200</v>
       </c>
       <c r="K43" s="3">
         <v>16876900</v>
@@ -2128,25 +2128,25 @@
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>3481400</v>
+        <v>3533400</v>
       </c>
       <c r="E44" s="3">
-        <v>4424600</v>
+        <v>4490600</v>
       </c>
       <c r="F44" s="3">
-        <v>3393700</v>
+        <v>3444300</v>
       </c>
       <c r="G44" s="3">
-        <v>2711600</v>
+        <v>2752100</v>
       </c>
       <c r="H44" s="3">
-        <v>2978600</v>
+        <v>3023000</v>
       </c>
       <c r="I44" s="3">
-        <v>2823400</v>
+        <v>2865500</v>
       </c>
       <c r="J44" s="3">
-        <v>2465500</v>
+        <v>2502300</v>
       </c>
       <c r="K44" s="3">
         <v>5847000</v>
@@ -2173,25 +2173,25 @@
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>437300</v>
+        <v>443800</v>
       </c>
       <c r="E45" s="3">
-        <v>395700</v>
+        <v>401600</v>
       </c>
       <c r="F45" s="3">
-        <v>292700</v>
+        <v>297100</v>
       </c>
       <c r="G45" s="3">
-        <v>370100</v>
+        <v>375600</v>
       </c>
       <c r="H45" s="3">
-        <v>190300</v>
+        <v>193200</v>
       </c>
       <c r="I45" s="3">
-        <v>267600</v>
+        <v>271600</v>
       </c>
       <c r="J45" s="3">
-        <v>394800</v>
+        <v>400700</v>
       </c>
       <c r="K45" s="3">
         <v>660300</v>
@@ -2218,25 +2218,25 @@
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>14957900</v>
+        <v>15181100</v>
       </c>
       <c r="E46" s="3">
-        <v>16773700</v>
+        <v>17024000</v>
       </c>
       <c r="F46" s="3">
-        <v>16870400</v>
+        <v>17122100</v>
       </c>
       <c r="G46" s="3">
-        <v>14456700</v>
+        <v>14672400</v>
       </c>
       <c r="H46" s="3">
-        <v>14854200</v>
+        <v>15075900</v>
       </c>
       <c r="I46" s="3">
-        <v>15554200</v>
+        <v>15786300</v>
       </c>
       <c r="J46" s="3">
-        <v>14806900</v>
+        <v>15027800</v>
       </c>
       <c r="K46" s="3">
         <v>16532700</v>
@@ -2263,25 +2263,25 @@
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>2014100</v>
+        <v>2044100</v>
       </c>
       <c r="E47" s="3">
-        <v>1893400</v>
+        <v>1921700</v>
       </c>
       <c r="F47" s="3">
-        <v>3919300</v>
+        <v>3977700</v>
       </c>
       <c r="G47" s="3">
-        <v>2940600</v>
+        <v>2984400</v>
       </c>
       <c r="H47" s="3">
-        <v>3013700</v>
+        <v>3058700</v>
       </c>
       <c r="I47" s="3">
-        <v>3266600</v>
+        <v>3315300</v>
       </c>
       <c r="J47" s="3">
-        <v>3377600</v>
+        <v>3428000</v>
       </c>
       <c r="K47" s="3">
         <v>1940600</v>
@@ -2308,25 +2308,25 @@
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>1786900</v>
+        <v>1813500</v>
       </c>
       <c r="E48" s="3">
-        <v>2133500</v>
+        <v>2165300</v>
       </c>
       <c r="F48" s="3">
-        <v>2077700</v>
+        <v>2108700</v>
       </c>
       <c r="G48" s="3">
-        <v>2061700</v>
+        <v>2092500</v>
       </c>
       <c r="H48" s="3">
-        <v>2155700</v>
+        <v>2187900</v>
       </c>
       <c r="I48" s="3">
-        <v>1240100</v>
+        <v>1258600</v>
       </c>
       <c r="J48" s="3">
-        <v>1240800</v>
+        <v>1259300</v>
       </c>
       <c r="K48" s="3">
         <v>3160000</v>
@@ -2353,25 +2353,25 @@
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>7748700</v>
+        <v>7864300</v>
       </c>
       <c r="E49" s="3">
-        <v>11061500</v>
+        <v>11226500</v>
       </c>
       <c r="F49" s="3">
-        <v>4397200</v>
+        <v>4462800</v>
       </c>
       <c r="G49" s="3">
-        <v>4208500</v>
+        <v>4271300</v>
       </c>
       <c r="H49" s="3">
-        <v>3641400</v>
+        <v>3695800</v>
       </c>
       <c r="I49" s="3">
-        <v>3642900</v>
+        <v>3697200</v>
       </c>
       <c r="J49" s="3">
-        <v>3528000</v>
+        <v>3580700</v>
       </c>
       <c r="K49" s="3">
         <v>11181200</v>
@@ -2488,25 +2488,25 @@
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>2159400</v>
+        <v>2191600</v>
       </c>
       <c r="E52" s="3">
-        <v>1871700</v>
+        <v>1899600</v>
       </c>
       <c r="F52" s="3">
-        <v>2230200</v>
+        <v>2263500</v>
       </c>
       <c r="G52" s="3">
-        <v>2537800</v>
+        <v>2575700</v>
       </c>
       <c r="H52" s="3">
-        <v>3008600</v>
+        <v>3053500</v>
       </c>
       <c r="I52" s="3">
-        <v>2234400</v>
+        <v>2267700</v>
       </c>
       <c r="J52" s="3">
-        <v>2127900</v>
+        <v>2159700</v>
       </c>
       <c r="K52" s="3">
         <v>1605000</v>
@@ -2578,25 +2578,25 @@
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>28666900</v>
+        <v>29094700</v>
       </c>
       <c r="E54" s="3">
-        <v>33733800</v>
+        <v>34237100</v>
       </c>
       <c r="F54" s="3">
-        <v>29494800</v>
+        <v>29934900</v>
       </c>
       <c r="G54" s="3">
-        <v>26205400</v>
+        <v>26596400</v>
       </c>
       <c r="H54" s="3">
-        <v>26673700</v>
+        <v>27071700</v>
       </c>
       <c r="I54" s="3">
-        <v>25938100</v>
+        <v>26325100</v>
       </c>
       <c r="J54" s="3">
-        <v>25081200</v>
+        <v>25455400</v>
       </c>
       <c r="K54" s="3">
         <v>26829400</v>
@@ -2661,25 +2661,25 @@
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>2679900</v>
+        <v>2719900</v>
       </c>
       <c r="E57" s="3">
-        <v>3709600</v>
+        <v>3764900</v>
       </c>
       <c r="F57" s="3">
-        <v>3443900</v>
+        <v>3495200</v>
       </c>
       <c r="G57" s="3">
-        <v>3087200</v>
+        <v>3133200</v>
       </c>
       <c r="H57" s="3">
-        <v>2934200</v>
+        <v>2978000</v>
       </c>
       <c r="I57" s="3">
-        <v>2884000</v>
+        <v>2927000</v>
       </c>
       <c r="J57" s="3">
-        <v>2540100</v>
+        <v>2578000</v>
       </c>
       <c r="K57" s="3">
         <v>4830700</v>
@@ -2706,25 +2706,25 @@
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>1919600</v>
+        <v>1948200</v>
       </c>
       <c r="E58" s="3">
-        <v>817400</v>
+        <v>829600</v>
       </c>
       <c r="F58" s="3">
-        <v>1140200</v>
+        <v>1157200</v>
       </c>
       <c r="G58" s="3">
-        <v>978400</v>
+        <v>993000</v>
       </c>
       <c r="H58" s="3">
-        <v>1131700</v>
+        <v>1148600</v>
       </c>
       <c r="I58" s="3">
-        <v>217600</v>
+        <v>220900</v>
       </c>
       <c r="J58" s="3">
-        <v>245600</v>
+        <v>249300</v>
       </c>
       <c r="K58" s="3">
         <v>1517000</v>
@@ -2751,25 +2751,25 @@
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>7888800</v>
+        <v>8006500</v>
       </c>
       <c r="E59" s="3">
-        <v>9526800</v>
+        <v>9668900</v>
       </c>
       <c r="F59" s="3">
-        <v>7668100</v>
+        <v>7782500</v>
       </c>
       <c r="G59" s="3">
-        <v>6967400</v>
+        <v>7071400</v>
       </c>
       <c r="H59" s="3">
-        <v>7208300</v>
+        <v>7315900</v>
       </c>
       <c r="I59" s="3">
-        <v>7602700</v>
+        <v>7716100</v>
       </c>
       <c r="J59" s="3">
-        <v>9431800</v>
+        <v>9572600</v>
       </c>
       <c r="K59" s="3">
         <v>11607000</v>
@@ -2796,25 +2796,25 @@
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>12488300</v>
+        <v>12674600</v>
       </c>
       <c r="E60" s="3">
-        <v>14053800</v>
+        <v>14263500</v>
       </c>
       <c r="F60" s="3">
-        <v>12252100</v>
+        <v>12434900</v>
       </c>
       <c r="G60" s="3">
-        <v>11033000</v>
+        <v>11197600</v>
       </c>
       <c r="H60" s="3">
-        <v>11274200</v>
+        <v>11442400</v>
       </c>
       <c r="I60" s="3">
-        <v>10704300</v>
+        <v>10864000</v>
       </c>
       <c r="J60" s="3">
-        <v>9605500</v>
+        <v>9748900</v>
       </c>
       <c r="K60" s="3">
         <v>9517800</v>
@@ -2841,25 +2841,25 @@
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>3323600</v>
+        <v>3373200</v>
       </c>
       <c r="E61" s="3">
-        <v>3258600</v>
+        <v>3307200</v>
       </c>
       <c r="F61" s="3">
-        <v>2829700</v>
+        <v>2871900</v>
       </c>
       <c r="G61" s="3">
-        <v>2829900</v>
+        <v>2872100</v>
       </c>
       <c r="H61" s="3">
-        <v>3460100</v>
+        <v>3511700</v>
       </c>
       <c r="I61" s="3">
-        <v>2979300</v>
+        <v>3023700</v>
       </c>
       <c r="J61" s="3">
-        <v>2943600</v>
+        <v>2987500</v>
       </c>
       <c r="K61" s="3">
         <v>1761200</v>
@@ -2886,25 +2886,25 @@
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>3454200</v>
+        <v>3505700</v>
       </c>
       <c r="E62" s="3">
-        <v>3556300</v>
+        <v>3609400</v>
       </c>
       <c r="F62" s="3">
-        <v>4076900</v>
+        <v>4137700</v>
       </c>
       <c r="G62" s="3">
-        <v>4122000</v>
+        <v>4183500</v>
       </c>
       <c r="H62" s="3">
-        <v>4037400</v>
+        <v>4097600</v>
       </c>
       <c r="I62" s="3">
-        <v>3783900</v>
+        <v>3840300</v>
       </c>
       <c r="J62" s="3">
-        <v>3115500</v>
+        <v>3162000</v>
       </c>
       <c r="K62" s="3">
         <v>2779400</v>
@@ -3066,25 +3066,25 @@
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>19144000</v>
+        <v>19429700</v>
       </c>
       <c r="E66" s="3">
-        <v>20722900</v>
+        <v>21032100</v>
       </c>
       <c r="F66" s="3">
-        <v>18996900</v>
+        <v>19280400</v>
       </c>
       <c r="G66" s="3">
-        <v>17840500</v>
+        <v>18106600</v>
       </c>
       <c r="H66" s="3">
-        <v>18706000</v>
+        <v>18985100</v>
       </c>
       <c r="I66" s="3">
-        <v>17543900</v>
+        <v>17805600</v>
       </c>
       <c r="J66" s="3">
-        <v>15726000</v>
+        <v>15960700</v>
       </c>
       <c r="K66" s="3">
         <v>14122200</v>
@@ -3310,25 +3310,25 @@
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>4870000</v>
+        <v>4942700</v>
       </c>
       <c r="E72" s="3">
-        <v>8223600</v>
+        <v>8346300</v>
       </c>
       <c r="F72" s="3">
-        <v>6458300</v>
+        <v>6554600</v>
       </c>
       <c r="G72" s="3">
-        <v>4628600</v>
+        <v>4697700</v>
       </c>
       <c r="H72" s="3">
-        <v>3750800</v>
+        <v>3806700</v>
       </c>
       <c r="I72" s="3">
-        <v>4398400</v>
+        <v>4464100</v>
       </c>
       <c r="J72" s="3">
-        <v>5359400</v>
+        <v>5439400</v>
       </c>
       <c r="K72" s="3">
         <v>8799400</v>
@@ -3490,25 +3490,25 @@
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>9522900</v>
+        <v>9665000</v>
       </c>
       <c r="E76" s="3">
-        <v>13010900</v>
+        <v>13205000</v>
       </c>
       <c r="F76" s="3">
-        <v>10497900</v>
+        <v>10654500</v>
       </c>
       <c r="G76" s="3">
-        <v>8364900</v>
+        <v>8489700</v>
       </c>
       <c r="H76" s="3">
-        <v>7967800</v>
+        <v>8086700</v>
       </c>
       <c r="I76" s="3">
-        <v>8394200</v>
+        <v>8519500</v>
       </c>
       <c r="J76" s="3">
-        <v>9355200</v>
+        <v>9494800</v>
       </c>
       <c r="K76" s="3">
         <v>12707200</v>
@@ -3630,25 +3630,25 @@
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>-2552300</v>
+        <v>-2590400</v>
       </c>
       <c r="E81" s="3">
-        <v>1807100</v>
+        <v>1834000</v>
       </c>
       <c r="F81" s="3">
-        <v>2190200</v>
+        <v>2222900</v>
       </c>
       <c r="G81" s="3">
-        <v>1687300</v>
+        <v>1712500</v>
       </c>
       <c r="H81" s="3">
-        <v>214500</v>
+        <v>217700</v>
       </c>
       <c r="I81" s="3">
-        <v>-630200</v>
+        <v>-639600</v>
       </c>
       <c r="J81" s="3">
-        <v>-3143900</v>
+        <v>-3190800</v>
       </c>
       <c r="K81" s="3">
         <v>78700</v>
@@ -3694,25 +3694,25 @@
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>1155500</v>
+        <v>1172800</v>
       </c>
       <c r="E83" s="3">
-        <v>1011600</v>
+        <v>1026700</v>
       </c>
       <c r="F83" s="3">
-        <v>835400</v>
+        <v>847900</v>
       </c>
       <c r="G83" s="3">
-        <v>823900</v>
+        <v>836200</v>
       </c>
       <c r="H83" s="3">
-        <v>829900</v>
+        <v>842300</v>
       </c>
       <c r="I83" s="3">
-        <v>696900</v>
+        <v>707300</v>
       </c>
       <c r="J83" s="3">
-        <v>815600</v>
+        <v>827800</v>
       </c>
       <c r="K83" s="3">
         <v>839000</v>
@@ -3964,25 +3964,25 @@
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>692700</v>
+        <v>703000</v>
       </c>
       <c r="E89" s="3">
-        <v>2978600</v>
+        <v>3023000</v>
       </c>
       <c r="F89" s="3">
-        <v>3770200</v>
+        <v>3826400</v>
       </c>
       <c r="G89" s="3">
-        <v>2792300</v>
+        <v>2834000</v>
       </c>
       <c r="H89" s="3">
-        <v>1628400</v>
+        <v>1652700</v>
       </c>
       <c r="I89" s="3">
-        <v>901600</v>
+        <v>915000</v>
       </c>
       <c r="J89" s="3">
-        <v>926600</v>
+        <v>940400</v>
       </c>
       <c r="K89" s="3">
         <v>1322800</v>
@@ -4028,25 +4028,25 @@
         <v>79</v>
       </c>
       <c r="D91" s="3">
-        <v>-318200</v>
+        <v>-322900</v>
       </c>
       <c r="E91" s="3">
-        <v>-432100</v>
+        <v>-438500</v>
       </c>
       <c r="F91" s="3">
-        <v>-353500</v>
+        <v>-358800</v>
       </c>
       <c r="G91" s="3">
-        <v>-433600</v>
+        <v>-440100</v>
       </c>
       <c r="H91" s="3">
-        <v>-493900</v>
+        <v>-501300</v>
       </c>
       <c r="I91" s="3">
-        <v>-383600</v>
+        <v>-389400</v>
       </c>
       <c r="J91" s="3">
-        <v>-374200</v>
+        <v>-379800</v>
       </c>
       <c r="K91" s="3">
         <v>-578700</v>
@@ -4163,25 +4163,25 @@
         <v>82</v>
       </c>
       <c r="D94" s="3">
-        <v>-840900</v>
+        <v>-853400</v>
       </c>
       <c r="E94" s="3">
-        <v>-3319700</v>
+        <v>-3369200</v>
       </c>
       <c r="F94" s="3">
-        <v>-1918900</v>
+        <v>-1947500</v>
       </c>
       <c r="G94" s="3">
-        <v>-1467000</v>
+        <v>-1488900</v>
       </c>
       <c r="H94" s="3">
-        <v>-341700</v>
+        <v>-346800</v>
       </c>
       <c r="I94" s="3">
-        <v>-398800</v>
+        <v>-404700</v>
       </c>
       <c r="J94" s="3">
-        <v>-1550900</v>
+        <v>-1574100</v>
       </c>
       <c r="K94" s="3">
         <v>-782100</v>
@@ -4227,25 +4227,25 @@
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>-867700</v>
+        <v>-880700</v>
       </c>
       <c r="E96" s="3">
-        <v>-803400</v>
+        <v>-815400</v>
       </c>
       <c r="F96" s="3">
-        <v>-642600</v>
+        <v>-652200</v>
       </c>
       <c r="G96" s="3">
-        <v>-481100</v>
+        <v>-488300</v>
       </c>
       <c r="H96" s="3">
-        <v>-318600</v>
+        <v>-323300</v>
       </c>
       <c r="I96" s="3">
-        <v>-330500</v>
+        <v>-335500</v>
       </c>
       <c r="J96" s="3">
-        <v>-330500</v>
+        <v>-335400</v>
       </c>
       <c r="K96" s="3">
         <v>-1157900</v>
@@ -4407,25 +4407,25 @@
         <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>97200</v>
+        <v>98600</v>
       </c>
       <c r="E100" s="3">
-        <v>-1537400</v>
+        <v>-1560300</v>
       </c>
       <c r="F100" s="3">
-        <v>-898200</v>
+        <v>-911600</v>
       </c>
       <c r="G100" s="3">
-        <v>-1205600</v>
+        <v>-1223600</v>
       </c>
       <c r="H100" s="3">
-        <v>-665900</v>
+        <v>-675900</v>
       </c>
       <c r="I100" s="3">
-        <v>-393500</v>
+        <v>-399300</v>
       </c>
       <c r="J100" s="3">
-        <v>528700</v>
+        <v>536600</v>
       </c>
       <c r="K100" s="3">
         <v>-1108700</v>
@@ -4452,25 +4452,25 @@
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>-253800</v>
+        <v>-257600</v>
       </c>
       <c r="E101" s="3">
-        <v>363200</v>
+        <v>368600</v>
       </c>
       <c r="F101" s="3">
-        <v>54300</v>
+        <v>55100</v>
       </c>
       <c r="G101" s="3">
-        <v>-261300</v>
+        <v>-265200</v>
       </c>
       <c r="H101" s="3">
-        <v>24900</v>
+        <v>25300</v>
       </c>
       <c r="I101" s="3">
-        <v>132400</v>
+        <v>134400</v>
       </c>
       <c r="J101" s="3">
-        <v>-8800</v>
+        <v>-8900</v>
       </c>
       <c r="K101" s="3">
         <v>260300</v>
@@ -4497,25 +4497,25 @@
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>-304900</v>
+        <v>-309400</v>
       </c>
       <c r="E102" s="3">
-        <v>-1515300</v>
+        <v>-1537900</v>
       </c>
       <c r="F102" s="3">
-        <v>1007400</v>
+        <v>1022400</v>
       </c>
       <c r="G102" s="3">
-        <v>-141600</v>
+        <v>-143700</v>
       </c>
       <c r="H102" s="3">
-        <v>645700</v>
+        <v>655300</v>
       </c>
       <c r="I102" s="3">
-        <v>241800</v>
+        <v>245400</v>
       </c>
       <c r="J102" s="3">
-        <v>-104400</v>
+        <v>-106000</v>
       </c>
       <c r="K102" s="3">
         <v>-307600</v>

--- a/AAII_Financials/Yearly/ERIC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ERIC_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="92">
   <si>
     <t>ERIC</t>
   </si>
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>25795200</v>
+        <v>26186700</v>
       </c>
       <c r="E8" s="3">
-        <v>26597900</v>
+        <v>26050000</v>
       </c>
       <c r="F8" s="3">
-        <v>22755200</v>
+        <v>25692400</v>
       </c>
       <c r="G8" s="3">
-        <v>22762600</v>
+        <v>28296400</v>
       </c>
       <c r="H8" s="3">
-        <v>22255800</v>
+        <v>24322300</v>
       </c>
       <c r="I8" s="3">
-        <v>20651600</v>
+        <v>23724700</v>
       </c>
       <c r="J8" s="3">
-        <v>20116800</v>
+        <v>25090100</v>
       </c>
       <c r="K8" s="3">
         <v>20802200</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>15568900</v>
+        <v>15805100</v>
       </c>
       <c r="E9" s="3">
-        <v>15481600</v>
+        <v>15162600</v>
       </c>
       <c r="F9" s="3">
-        <v>12860100</v>
+        <v>14520000</v>
       </c>
       <c r="G9" s="3">
-        <v>13511300</v>
+        <v>16796000</v>
       </c>
       <c r="H9" s="3">
-        <v>13914300</v>
+        <v>15206300</v>
       </c>
       <c r="I9" s="3">
-        <v>13389800</v>
+        <v>15382300</v>
       </c>
       <c r="J9" s="3">
-        <v>14908900</v>
+        <v>18594700</v>
       </c>
       <c r="K9" s="3">
         <v>14312800</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>10226400</v>
+        <v>10381600</v>
       </c>
       <c r="E10" s="3">
-        <v>11116300</v>
+        <v>10887300</v>
       </c>
       <c r="F10" s="3">
-        <v>9895100</v>
+        <v>11172400</v>
       </c>
       <c r="G10" s="3">
-        <v>9251300</v>
+        <v>11500300</v>
       </c>
       <c r="H10" s="3">
-        <v>8341500</v>
+        <v>9116100</v>
       </c>
       <c r="I10" s="3">
-        <v>7261800</v>
+        <v>8342400</v>
       </c>
       <c r="J10" s="3">
-        <v>5207900</v>
+        <v>6495400</v>
       </c>
       <c r="K10" s="3">
         <v>6489400</v>
@@ -880,25 +880,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>4724400</v>
+        <v>4796100</v>
       </c>
       <c r="E12" s="3">
-        <v>4627500</v>
+        <v>4526400</v>
       </c>
       <c r="F12" s="3">
-        <v>4107700</v>
+        <v>4638000</v>
       </c>
       <c r="G12" s="3">
-        <v>3849700</v>
+        <v>4785600</v>
       </c>
       <c r="H12" s="3">
-        <v>3768200</v>
+        <v>4118100</v>
       </c>
       <c r="I12" s="3">
-        <v>3684500</v>
+        <v>4204200</v>
       </c>
       <c r="J12" s="3">
-        <v>3485100</v>
+        <v>4029000</v>
       </c>
       <c r="K12" s="3">
         <v>2728000</v>
@@ -970,25 +970,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>3763000</v>
+        <v>3850400</v>
       </c>
       <c r="E14" s="3">
-        <v>397200</v>
+        <v>279100</v>
       </c>
       <c r="F14" s="3">
-        <v>67800</v>
+        <v>-33100</v>
       </c>
       <c r="G14" s="3">
-        <v>141400</v>
+        <v>179600</v>
       </c>
       <c r="H14" s="3">
-        <v>174800</v>
+        <v>1153000</v>
       </c>
       <c r="I14" s="3">
-        <v>828500</v>
+        <v>988000</v>
       </c>
       <c r="J14" s="3">
-        <v>2543600</v>
+        <v>3121200</v>
       </c>
       <c r="K14" s="3">
         <v>706600</v>
@@ -1015,25 +1015,25 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>755000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>585700</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>535100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>570500</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>493000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>524600</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>704900</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1076,25 +1076,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>27786200</v>
+        <v>24318400</v>
       </c>
       <c r="E17" s="3">
-        <v>23951300</v>
+        <v>23145800</v>
       </c>
       <c r="F17" s="3">
-        <v>19642300</v>
+        <v>22153100</v>
       </c>
       <c r="G17" s="3">
-        <v>20038800</v>
+        <v>24726400</v>
       </c>
       <c r="H17" s="3">
-        <v>21221100</v>
+        <v>22002700</v>
       </c>
       <c r="I17" s="3">
-        <v>20529900</v>
+        <v>22603500</v>
       </c>
       <c r="J17" s="3">
-        <v>23519900</v>
+        <v>26216300</v>
       </c>
       <c r="K17" s="3">
         <v>20312500</v>
@@ -1121,25 +1121,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-1990900</v>
+        <v>1868300</v>
       </c>
       <c r="E18" s="3">
-        <v>2646600</v>
+        <v>2904200</v>
       </c>
       <c r="F18" s="3">
-        <v>3112900</v>
+        <v>3539300</v>
       </c>
       <c r="G18" s="3">
-        <v>2723800</v>
+        <v>3570000</v>
       </c>
       <c r="H18" s="3">
-        <v>1034700</v>
+        <v>2319700</v>
       </c>
       <c r="I18" s="3">
-        <v>121700</v>
+        <v>1121200</v>
       </c>
       <c r="J18" s="3">
-        <v>-3403100</v>
+        <v>-1126100</v>
       </c>
       <c r="K18" s="3">
         <v>489800</v>
@@ -1185,25 +1185,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-24200</v>
+        <v>252300</v>
       </c>
       <c r="E20" s="3">
-        <v>-95500</v>
+        <v>195300</v>
       </c>
       <c r="F20" s="3">
-        <v>-154700</v>
+        <v>272200</v>
       </c>
       <c r="G20" s="3">
-        <v>75100</v>
+        <v>-8000</v>
       </c>
       <c r="H20" s="3">
-        <v>13800</v>
+        <v>171100</v>
       </c>
       <c r="I20" s="3">
-        <v>-167300</v>
+        <v>202200</v>
       </c>
       <c r="J20" s="3">
-        <v>-18400</v>
+        <v>63400</v>
       </c>
       <c r="K20" s="3">
         <v>-88600</v>
@@ -1230,25 +1230,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-850600</v>
+        <v>2371100</v>
       </c>
       <c r="E21" s="3">
-        <v>3570600</v>
+        <v>3294500</v>
       </c>
       <c r="F21" s="3">
-        <v>3800100</v>
+        <v>3802200</v>
       </c>
       <c r="G21" s="3">
-        <v>3629200</v>
+        <v>4148400</v>
       </c>
       <c r="H21" s="3">
-        <v>1884900</v>
+        <v>2641700</v>
       </c>
       <c r="I21" s="3">
-        <v>656700</v>
+        <v>1443600</v>
       </c>
       <c r="J21" s="3">
-        <v>-2599500</v>
+        <v>-484600</v>
       </c>
       <c r="K21" s="3">
         <v>1243700</v>
@@ -1275,25 +1275,25 @@
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>269000</v>
+        <v>273100</v>
       </c>
       <c r="E22" s="3">
-        <v>140700</v>
+        <v>137800</v>
       </c>
       <c r="F22" s="3">
-        <v>93200</v>
+        <v>105200</v>
       </c>
       <c r="G22" s="3">
-        <v>133500</v>
+        <v>166000</v>
       </c>
       <c r="H22" s="3">
-        <v>190300</v>
+        <v>189800</v>
       </c>
       <c r="I22" s="3">
-        <v>97700</v>
+        <v>160900</v>
       </c>
       <c r="J22" s="3">
-        <v>100600</v>
+        <v>139800</v>
       </c>
       <c r="K22" s="3">
         <v>127900</v>
@@ -1320,25 +1320,25 @@
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>-2284100</v>
+        <v>-2318800</v>
       </c>
       <c r="E23" s="3">
-        <v>2410500</v>
+        <v>2360800</v>
       </c>
       <c r="F23" s="3">
-        <v>2865000</v>
+        <v>3234900</v>
       </c>
       <c r="G23" s="3">
-        <v>2665400</v>
+        <v>3313400</v>
       </c>
       <c r="H23" s="3">
-        <v>858200</v>
+        <v>937900</v>
       </c>
       <c r="I23" s="3">
-        <v>-143300</v>
+        <v>-164600</v>
       </c>
       <c r="J23" s="3">
-        <v>-3522100</v>
+        <v>-4392800</v>
       </c>
       <c r="K23" s="3">
         <v>273300</v>
@@ -1365,25 +1365,25 @@
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>272800</v>
+        <v>276900</v>
       </c>
       <c r="E24" s="3">
-        <v>538400</v>
+        <v>527300</v>
       </c>
       <c r="F24" s="3">
-        <v>614100</v>
+        <v>693400</v>
       </c>
       <c r="G24" s="3">
-        <v>939200</v>
+        <v>1167600</v>
       </c>
       <c r="H24" s="3">
-        <v>678000</v>
+        <v>741000</v>
       </c>
       <c r="I24" s="3">
-        <v>471400</v>
+        <v>541600</v>
       </c>
       <c r="J24" s="3">
-        <v>-345300</v>
+        <v>-430600</v>
       </c>
       <c r="K24" s="3">
         <v>177700</v>
@@ -1455,25 +1455,25 @@
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>-2556900</v>
+        <v>-2595700</v>
       </c>
       <c r="E26" s="3">
-        <v>1872000</v>
+        <v>1833500</v>
       </c>
       <c r="F26" s="3">
-        <v>2250900</v>
+        <v>2541400</v>
       </c>
       <c r="G26" s="3">
-        <v>1726200</v>
+        <v>2145800</v>
       </c>
       <c r="H26" s="3">
-        <v>180200</v>
+        <v>197000</v>
       </c>
       <c r="I26" s="3">
-        <v>-614700</v>
+        <v>-706200</v>
       </c>
       <c r="J26" s="3">
-        <v>-3176800</v>
+        <v>-3962200</v>
       </c>
       <c r="K26" s="3">
         <v>95600</v>
@@ -1500,25 +1500,25 @@
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>-2590400</v>
+        <v>-2629700</v>
       </c>
       <c r="E27" s="3">
-        <v>1834000</v>
+        <v>1796200</v>
       </c>
       <c r="F27" s="3">
-        <v>2222900</v>
+        <v>2509800</v>
       </c>
       <c r="G27" s="3">
-        <v>1712500</v>
+        <v>2128800</v>
       </c>
       <c r="H27" s="3">
-        <v>217700</v>
+        <v>238000</v>
       </c>
       <c r="I27" s="3">
-        <v>-639600</v>
+        <v>-734800</v>
       </c>
       <c r="J27" s="3">
-        <v>-3190800</v>
+        <v>-3979700</v>
       </c>
       <c r="K27" s="3">
         <v>78700</v>
@@ -1725,25 +1725,25 @@
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>24200</v>
+        <v>-252300</v>
       </c>
       <c r="E32" s="3">
-        <v>95500</v>
+        <v>-195300</v>
       </c>
       <c r="F32" s="3">
-        <v>154700</v>
+        <v>-272200</v>
       </c>
       <c r="G32" s="3">
-        <v>-75100</v>
+        <v>8000</v>
       </c>
       <c r="H32" s="3">
-        <v>-13800</v>
+        <v>-171100</v>
       </c>
       <c r="I32" s="3">
-        <v>167300</v>
+        <v>-202200</v>
       </c>
       <c r="J32" s="3">
-        <v>18400</v>
+        <v>-63400</v>
       </c>
       <c r="K32" s="3">
         <v>88600</v>
@@ -1770,25 +1770,25 @@
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>-2590400</v>
+        <v>-2629700</v>
       </c>
       <c r="E33" s="3">
-        <v>1834000</v>
+        <v>1796200</v>
       </c>
       <c r="F33" s="3">
-        <v>2222900</v>
+        <v>2509800</v>
       </c>
       <c r="G33" s="3">
-        <v>1712500</v>
+        <v>2128800</v>
       </c>
       <c r="H33" s="3">
-        <v>217700</v>
+        <v>238000</v>
       </c>
       <c r="I33" s="3">
-        <v>-639600</v>
+        <v>-734800</v>
       </c>
       <c r="J33" s="3">
-        <v>-3190800</v>
+        <v>-3979700</v>
       </c>
       <c r="K33" s="3">
         <v>78700</v>
@@ -1860,25 +1860,25 @@
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>-2590400</v>
+        <v>-2629700</v>
       </c>
       <c r="E35" s="3">
-        <v>1834000</v>
+        <v>1796200</v>
       </c>
       <c r="F35" s="3">
-        <v>2222900</v>
+        <v>2509800</v>
       </c>
       <c r="G35" s="3">
-        <v>1712500</v>
+        <v>2128800</v>
       </c>
       <c r="H35" s="3">
-        <v>217700</v>
+        <v>238000</v>
       </c>
       <c r="I35" s="3">
-        <v>-639600</v>
+        <v>-734800</v>
       </c>
       <c r="J35" s="3">
-        <v>-3190800</v>
+        <v>-3979700</v>
       </c>
       <c r="K35" s="3">
         <v>78700</v>
@@ -1993,25 +1993,25 @@
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>3446900</v>
+        <v>3499200</v>
       </c>
       <c r="E41" s="3">
-        <v>3756300</v>
+        <v>3678900</v>
       </c>
       <c r="F41" s="3">
-        <v>5294200</v>
+        <v>5977600</v>
       </c>
       <c r="G41" s="3">
-        <v>4271800</v>
+        <v>5310300</v>
       </c>
       <c r="H41" s="3">
-        <v>4415500</v>
+        <v>4825500</v>
       </c>
       <c r="I41" s="3">
-        <v>3760200</v>
+        <v>4319700</v>
       </c>
       <c r="J41" s="3">
-        <v>3514800</v>
+        <v>4383800</v>
       </c>
       <c r="K41" s="3">
         <v>6980700</v>
@@ -2038,25 +2038,25 @@
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>938800</v>
+        <v>953000</v>
       </c>
       <c r="E42" s="3">
-        <v>855700</v>
+        <v>838100</v>
       </c>
       <c r="F42" s="3">
-        <v>1266700</v>
+        <v>1430200</v>
       </c>
       <c r="G42" s="3">
-        <v>668000</v>
+        <v>830400</v>
       </c>
       <c r="H42" s="3">
-        <v>662000</v>
+        <v>723500</v>
       </c>
       <c r="I42" s="3">
-        <v>648900</v>
+        <v>745500</v>
       </c>
       <c r="J42" s="3">
-        <v>657500</v>
+        <v>820100</v>
       </c>
       <c r="K42" s="3">
         <v>1258100</v>
@@ -2083,25 +2083,25 @@
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>6818300</v>
+        <v>6921800</v>
       </c>
       <c r="E43" s="3">
-        <v>7519800</v>
+        <v>7364900</v>
       </c>
       <c r="F43" s="3">
-        <v>6819900</v>
+        <v>7700200</v>
       </c>
       <c r="G43" s="3">
-        <v>6604900</v>
+        <v>8210600</v>
       </c>
       <c r="H43" s="3">
-        <v>6782200</v>
+        <v>7411900</v>
       </c>
       <c r="I43" s="3">
-        <v>8240000</v>
+        <v>9778300</v>
       </c>
       <c r="J43" s="3">
-        <v>14275200</v>
+        <v>10418200</v>
       </c>
       <c r="K43" s="3">
         <v>16876900</v>
@@ -2128,25 +2128,25 @@
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>3533400</v>
+        <v>3587000</v>
       </c>
       <c r="E44" s="3">
-        <v>4490600</v>
+        <v>4398100</v>
       </c>
       <c r="F44" s="3">
-        <v>3444300</v>
+        <v>3888900</v>
       </c>
       <c r="G44" s="3">
-        <v>2752100</v>
+        <v>3421200</v>
       </c>
       <c r="H44" s="3">
-        <v>3023000</v>
+        <v>3303700</v>
       </c>
       <c r="I44" s="3">
-        <v>2865500</v>
+        <v>3291900</v>
       </c>
       <c r="J44" s="3">
-        <v>2502300</v>
+        <v>3121000</v>
       </c>
       <c r="K44" s="3">
         <v>5847000</v>
@@ -2173,25 +2173,25 @@
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>443800</v>
+        <v>196800</v>
       </c>
       <c r="E45" s="3">
-        <v>401600</v>
+        <v>152900</v>
       </c>
       <c r="F45" s="3">
-        <v>297100</v>
+        <v>82200</v>
       </c>
       <c r="G45" s="3">
-        <v>375600</v>
+        <v>240800</v>
       </c>
       <c r="H45" s="3">
-        <v>193200</v>
-      </c>
-      <c r="I45" s="3">
-        <v>271600</v>
-      </c>
-      <c r="J45" s="3">
-        <v>400700</v>
+        <v>59300</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="K45" s="3">
         <v>660300</v>
@@ -2218,25 +2218,25 @@
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>15181100</v>
+        <v>15411400</v>
       </c>
       <c r="E46" s="3">
-        <v>17024000</v>
+        <v>16673300</v>
       </c>
       <c r="F46" s="3">
-        <v>17122100</v>
+        <v>19332300</v>
       </c>
       <c r="G46" s="3">
-        <v>14672400</v>
+        <v>18239400</v>
       </c>
       <c r="H46" s="3">
-        <v>15075900</v>
+        <v>16475700</v>
       </c>
       <c r="I46" s="3">
-        <v>15786300</v>
+        <v>18135400</v>
       </c>
       <c r="J46" s="3">
-        <v>15027800</v>
+        <v>18743000</v>
       </c>
       <c r="K46" s="3">
         <v>16532700</v>
@@ -2263,25 +2263,25 @@
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>2044100</v>
+        <v>1309800</v>
       </c>
       <c r="E47" s="3">
-        <v>1921700</v>
+        <v>1186200</v>
       </c>
       <c r="F47" s="3">
-        <v>3977700</v>
+        <v>3740800</v>
       </c>
       <c r="G47" s="3">
-        <v>2984400</v>
+        <v>2971700</v>
       </c>
       <c r="H47" s="3">
-        <v>3058700</v>
+        <v>2499600</v>
       </c>
       <c r="I47" s="3">
-        <v>3315300</v>
+        <v>2937800</v>
       </c>
       <c r="J47" s="3">
-        <v>3428000</v>
+        <v>3299400</v>
       </c>
       <c r="K47" s="3">
         <v>1940600</v>
@@ -2308,25 +2308,25 @@
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>1813500</v>
+        <v>1841100</v>
       </c>
       <c r="E48" s="3">
-        <v>2165300</v>
+        <v>2120700</v>
       </c>
       <c r="F48" s="3">
-        <v>2108700</v>
+        <v>2380900</v>
       </c>
       <c r="G48" s="3">
-        <v>2092500</v>
+        <v>2601200</v>
       </c>
       <c r="H48" s="3">
-        <v>2187900</v>
+        <v>2391100</v>
       </c>
       <c r="I48" s="3">
-        <v>1258600</v>
+        <v>1445800</v>
       </c>
       <c r="J48" s="3">
-        <v>1259300</v>
+        <v>1570700</v>
       </c>
       <c r="K48" s="3">
         <v>3160000</v>
@@ -2353,25 +2353,25 @@
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>7864300</v>
+        <v>7518500</v>
       </c>
       <c r="E49" s="3">
-        <v>11226500</v>
+        <v>10639800</v>
       </c>
       <c r="F49" s="3">
-        <v>4462800</v>
+        <v>4648700</v>
       </c>
       <c r="G49" s="3">
-        <v>4271300</v>
+        <v>4840100</v>
       </c>
       <c r="H49" s="3">
-        <v>3695800</v>
+        <v>3606500</v>
       </c>
       <c r="I49" s="3">
-        <v>3697200</v>
+        <v>3770600</v>
       </c>
       <c r="J49" s="3">
-        <v>3580700</v>
+        <v>3904800</v>
       </c>
       <c r="K49" s="3">
         <v>11181200</v>
@@ -2488,25 +2488,25 @@
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>2191600</v>
+        <v>631400</v>
       </c>
       <c r="E52" s="3">
-        <v>1899600</v>
+        <v>656100</v>
       </c>
       <c r="F52" s="3">
-        <v>2263500</v>
+        <v>687600</v>
       </c>
       <c r="G52" s="3">
-        <v>2575700</v>
+        <v>589600</v>
       </c>
       <c r="H52" s="3">
-        <v>3053500</v>
+        <v>601000</v>
       </c>
       <c r="I52" s="3">
-        <v>2267700</v>
+        <v>738100</v>
       </c>
       <c r="J52" s="3">
-        <v>2159700</v>
+        <v>720400</v>
       </c>
       <c r="K52" s="3">
         <v>1605000</v>
@@ -2578,25 +2578,25 @@
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>29094700</v>
+        <v>29536200</v>
       </c>
       <c r="E54" s="3">
-        <v>34237100</v>
+        <v>33531800</v>
       </c>
       <c r="F54" s="3">
-        <v>29934900</v>
+        <v>33798900</v>
       </c>
       <c r="G54" s="3">
-        <v>26596400</v>
+        <v>33062100</v>
       </c>
       <c r="H54" s="3">
-        <v>27071700</v>
+        <v>29585400</v>
       </c>
       <c r="I54" s="3">
-        <v>26325100</v>
+        <v>30242500</v>
       </c>
       <c r="J54" s="3">
-        <v>25455400</v>
+        <v>31748600</v>
       </c>
       <c r="K54" s="3">
         <v>26829400</v>
@@ -2661,25 +2661,25 @@
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>2719900</v>
+        <v>2761100</v>
       </c>
       <c r="E57" s="3">
-        <v>3764900</v>
+        <v>3687300</v>
       </c>
       <c r="F57" s="3">
-        <v>3495200</v>
+        <v>3946400</v>
       </c>
       <c r="G57" s="3">
-        <v>3133200</v>
+        <v>3894900</v>
       </c>
       <c r="H57" s="3">
-        <v>2978000</v>
+        <v>3254500</v>
       </c>
       <c r="I57" s="3">
-        <v>2927000</v>
+        <v>3362600</v>
       </c>
       <c r="J57" s="3">
-        <v>2578000</v>
+        <v>3215400</v>
       </c>
       <c r="K57" s="3">
         <v>4830700</v>
@@ -2706,25 +2706,25 @@
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>1948200</v>
+        <v>1977800</v>
       </c>
       <c r="E58" s="3">
-        <v>829600</v>
+        <v>813300</v>
       </c>
       <c r="F58" s="3">
-        <v>1157200</v>
+        <v>1316600</v>
       </c>
       <c r="G58" s="3">
-        <v>993000</v>
+        <v>1246600</v>
       </c>
       <c r="H58" s="3">
-        <v>1148600</v>
+        <v>1272900</v>
       </c>
       <c r="I58" s="3">
-        <v>220900</v>
+        <v>253700</v>
       </c>
       <c r="J58" s="3">
-        <v>249300</v>
+        <v>310900</v>
       </c>
       <c r="K58" s="3">
         <v>1517000</v>
@@ -2751,25 +2751,25 @@
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>8006500</v>
+        <v>5380100</v>
       </c>
       <c r="E59" s="3">
-        <v>9668900</v>
+        <v>5931700</v>
       </c>
       <c r="F59" s="3">
-        <v>7782500</v>
+        <v>5245900</v>
       </c>
       <c r="G59" s="3">
-        <v>7071400</v>
+        <v>5065100</v>
       </c>
       <c r="H59" s="3">
-        <v>7315900</v>
+        <v>4616600</v>
       </c>
       <c r="I59" s="3">
-        <v>7716100</v>
+        <v>8864300</v>
       </c>
       <c r="J59" s="3">
-        <v>9572600</v>
+        <v>8632700</v>
       </c>
       <c r="K59" s="3">
         <v>11607000</v>
@@ -2796,25 +2796,25 @@
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>12674600</v>
+        <v>12867000</v>
       </c>
       <c r="E60" s="3">
-        <v>14263500</v>
+        <v>13969600</v>
       </c>
       <c r="F60" s="3">
-        <v>12434900</v>
+        <v>14040100</v>
       </c>
       <c r="G60" s="3">
-        <v>11197600</v>
+        <v>13919900</v>
       </c>
       <c r="H60" s="3">
-        <v>11442400</v>
+        <v>12504900</v>
       </c>
       <c r="I60" s="3">
-        <v>10864000</v>
+        <v>12480700</v>
       </c>
       <c r="J60" s="3">
-        <v>9748900</v>
+        <v>12159000</v>
       </c>
       <c r="K60" s="3">
         <v>9517800</v>
@@ -2841,25 +2841,25 @@
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>3373200</v>
+        <v>3424400</v>
       </c>
       <c r="E61" s="3">
-        <v>3307200</v>
+        <v>3239100</v>
       </c>
       <c r="F61" s="3">
-        <v>2871900</v>
+        <v>3242600</v>
       </c>
       <c r="G61" s="3">
-        <v>2872100</v>
+        <v>3570300</v>
       </c>
       <c r="H61" s="3">
-        <v>3511700</v>
+        <v>3837800</v>
       </c>
       <c r="I61" s="3">
-        <v>3023700</v>
+        <v>3473700</v>
       </c>
       <c r="J61" s="3">
-        <v>2987500</v>
+        <v>3726100</v>
       </c>
       <c r="K61" s="3">
         <v>1761200</v>
@@ -2886,25 +2886,25 @@
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>3505700</v>
+        <v>565000</v>
       </c>
       <c r="E62" s="3">
-        <v>3609400</v>
+        <v>451300</v>
       </c>
       <c r="F62" s="3">
-        <v>4137700</v>
+        <v>587100</v>
       </c>
       <c r="G62" s="3">
-        <v>4183500</v>
+        <v>519800</v>
       </c>
       <c r="H62" s="3">
-        <v>4097600</v>
+        <v>513100</v>
       </c>
       <c r="I62" s="3">
-        <v>3840300</v>
+        <v>1104700</v>
       </c>
       <c r="J62" s="3">
-        <v>3162000</v>
+        <v>778400</v>
       </c>
       <c r="K62" s="3">
         <v>2779400</v>
@@ -3066,25 +3066,25 @@
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>19429700</v>
+        <v>19850300</v>
       </c>
       <c r="E66" s="3">
-        <v>21032100</v>
+        <v>20743700</v>
       </c>
       <c r="F66" s="3">
-        <v>19280400</v>
+        <v>21954500</v>
       </c>
       <c r="G66" s="3">
-        <v>18106600</v>
+        <v>22690800</v>
       </c>
       <c r="H66" s="3">
-        <v>18985100</v>
+        <v>20820800</v>
       </c>
       <c r="I66" s="3">
-        <v>17805600</v>
+        <v>20366100</v>
       </c>
       <c r="J66" s="3">
-        <v>15960700</v>
+        <v>19828800</v>
       </c>
       <c r="K66" s="3">
         <v>14122200</v>
@@ -3310,25 +3310,25 @@
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>4942700</v>
+        <v>5017700</v>
       </c>
       <c r="E72" s="3">
-        <v>8346300</v>
+        <v>8174400</v>
       </c>
       <c r="F72" s="3">
-        <v>6554600</v>
+        <v>7400700</v>
       </c>
       <c r="G72" s="3">
-        <v>4697700</v>
+        <v>5839700</v>
       </c>
       <c r="H72" s="3">
-        <v>3806700</v>
+        <v>4160200</v>
       </c>
       <c r="I72" s="3">
-        <v>4464100</v>
+        <v>5019800</v>
       </c>
       <c r="J72" s="3">
-        <v>5439400</v>
+        <v>6824900</v>
       </c>
       <c r="K72" s="3">
         <v>8799400</v>
@@ -3490,25 +3490,25 @@
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>9665000</v>
+        <v>9811700</v>
       </c>
       <c r="E76" s="3">
-        <v>13205000</v>
+        <v>12933000</v>
       </c>
       <c r="F76" s="3">
-        <v>10654500</v>
+        <v>12029800</v>
       </c>
       <c r="G76" s="3">
-        <v>8489700</v>
+        <v>10553600</v>
       </c>
       <c r="H76" s="3">
-        <v>8086700</v>
+        <v>8837500</v>
       </c>
       <c r="I76" s="3">
-        <v>8519500</v>
+        <v>9787300</v>
       </c>
       <c r="J76" s="3">
-        <v>9494800</v>
+        <v>11842100</v>
       </c>
       <c r="K76" s="3">
         <v>12707200</v>
@@ -3630,25 +3630,25 @@
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>-2590400</v>
+        <v>-2629700</v>
       </c>
       <c r="E81" s="3">
-        <v>1834000</v>
+        <v>1796200</v>
       </c>
       <c r="F81" s="3">
-        <v>2222900</v>
+        <v>2509800</v>
       </c>
       <c r="G81" s="3">
-        <v>1712500</v>
+        <v>2128800</v>
       </c>
       <c r="H81" s="3">
-        <v>217700</v>
+        <v>238000</v>
       </c>
       <c r="I81" s="3">
-        <v>-639600</v>
+        <v>-734800</v>
       </c>
       <c r="J81" s="3">
-        <v>-3190800</v>
+        <v>-3979700</v>
       </c>
       <c r="K81" s="3">
         <v>78700</v>
@@ -3694,25 +3694,25 @@
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>1172800</v>
+        <v>666100</v>
       </c>
       <c r="E83" s="3">
-        <v>1026700</v>
+        <v>629800</v>
       </c>
       <c r="F83" s="3">
-        <v>847900</v>
+        <v>658100</v>
       </c>
       <c r="G83" s="3">
-        <v>836200</v>
+        <v>729200</v>
       </c>
       <c r="H83" s="3">
-        <v>842300</v>
+        <v>648800</v>
       </c>
       <c r="I83" s="3">
-        <v>707300</v>
+        <v>368500</v>
       </c>
       <c r="J83" s="3">
-        <v>827800</v>
+        <v>501200</v>
       </c>
       <c r="K83" s="3">
         <v>839000</v>
@@ -3964,25 +3964,25 @@
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>703000</v>
+        <v>713700</v>
       </c>
       <c r="E89" s="3">
-        <v>3023000</v>
+        <v>2960800</v>
       </c>
       <c r="F89" s="3">
-        <v>3826400</v>
+        <v>4320300</v>
       </c>
       <c r="G89" s="3">
-        <v>2834000</v>
+        <v>3522900</v>
       </c>
       <c r="H89" s="3">
-        <v>1652700</v>
+        <v>1806200</v>
       </c>
       <c r="I89" s="3">
-        <v>915000</v>
+        <v>1051200</v>
       </c>
       <c r="J89" s="3">
-        <v>940400</v>
+        <v>1172900</v>
       </c>
       <c r="K89" s="3">
         <v>1322800</v>
@@ -4028,25 +4028,25 @@
         <v>79</v>
       </c>
       <c r="D91" s="3">
-        <v>-322900</v>
+        <v>-319200</v>
       </c>
       <c r="E91" s="3">
-        <v>-438500</v>
+        <v>-425000</v>
       </c>
       <c r="F91" s="3">
-        <v>-358800</v>
+        <v>-405100</v>
       </c>
       <c r="G91" s="3">
-        <v>-440100</v>
+        <v>-547100</v>
       </c>
       <c r="H91" s="3">
-        <v>-501300</v>
+        <v>-539200</v>
       </c>
       <c r="I91" s="3">
-        <v>-389400</v>
+        <v>-447300</v>
       </c>
       <c r="J91" s="3">
-        <v>-379800</v>
+        <v>-473600</v>
       </c>
       <c r="K91" s="3">
         <v>-578700</v>
@@ -4163,25 +4163,25 @@
         <v>82</v>
       </c>
       <c r="D94" s="3">
-        <v>-853400</v>
+        <v>-866400</v>
       </c>
       <c r="E94" s="3">
-        <v>-3369200</v>
+        <v>-3299800</v>
       </c>
       <c r="F94" s="3">
-        <v>-1947500</v>
+        <v>-2198900</v>
       </c>
       <c r="G94" s="3">
-        <v>-1488900</v>
+        <v>-1850900</v>
       </c>
       <c r="H94" s="3">
-        <v>-346800</v>
+        <v>-379000</v>
       </c>
       <c r="I94" s="3">
-        <v>-404700</v>
+        <v>-465000</v>
       </c>
       <c r="J94" s="3">
-        <v>-1574100</v>
+        <v>-1963200</v>
       </c>
       <c r="K94" s="3">
         <v>-782100</v>
@@ -4227,25 +4227,25 @@
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>-880700</v>
+        <v>894000</v>
       </c>
       <c r="E96" s="3">
-        <v>-815400</v>
+        <v>798600</v>
       </c>
       <c r="F96" s="3">
-        <v>-652200</v>
+        <v>736300</v>
       </c>
       <c r="G96" s="3">
-        <v>-488300</v>
+        <v>607000</v>
       </c>
       <c r="H96" s="3">
-        <v>-323300</v>
+        <v>353400</v>
       </c>
       <c r="I96" s="3">
-        <v>-335500</v>
+        <v>369900</v>
       </c>
       <c r="J96" s="3">
-        <v>-335400</v>
+        <v>399800</v>
       </c>
       <c r="K96" s="3">
         <v>-1157900</v>
@@ -4407,25 +4407,25 @@
         <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>98600</v>
+        <v>100100</v>
       </c>
       <c r="E100" s="3">
-        <v>-1560300</v>
+        <v>-1528200</v>
       </c>
       <c r="F100" s="3">
-        <v>-911600</v>
+        <v>-1029300</v>
       </c>
       <c r="G100" s="3">
-        <v>-1223600</v>
+        <v>-1521100</v>
       </c>
       <c r="H100" s="3">
-        <v>-675900</v>
+        <v>-738600</v>
       </c>
       <c r="I100" s="3">
-        <v>-399300</v>
+        <v>-458800</v>
       </c>
       <c r="J100" s="3">
-        <v>536600</v>
+        <v>669200</v>
       </c>
       <c r="K100" s="3">
         <v>-1108700</v>
@@ -4452,25 +4452,25 @@
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>-257600</v>
+        <v>-261500</v>
       </c>
       <c r="E101" s="3">
-        <v>368600</v>
+        <v>361000</v>
       </c>
       <c r="F101" s="3">
-        <v>55100</v>
+        <v>62300</v>
       </c>
       <c r="G101" s="3">
-        <v>-265200</v>
+        <v>-329600</v>
       </c>
       <c r="H101" s="3">
-        <v>25300</v>
+        <v>27600</v>
       </c>
       <c r="I101" s="3">
-        <v>134400</v>
+        <v>154400</v>
       </c>
       <c r="J101" s="3">
-        <v>-8900</v>
+        <v>-11100</v>
       </c>
       <c r="K101" s="3">
         <v>260300</v>
@@ -4497,25 +4497,25 @@
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>-309400</v>
+        <v>-314100</v>
       </c>
       <c r="E102" s="3">
-        <v>-1537900</v>
+        <v>-1506200</v>
       </c>
       <c r="F102" s="3">
-        <v>1022400</v>
+        <v>1154400</v>
       </c>
       <c r="G102" s="3">
-        <v>-143700</v>
+        <v>-178600</v>
       </c>
       <c r="H102" s="3">
-        <v>655300</v>
+        <v>716100</v>
       </c>
       <c r="I102" s="3">
-        <v>245400</v>
+        <v>281900</v>
       </c>
       <c r="J102" s="3">
-        <v>-106000</v>
+        <v>-132200</v>
       </c>
       <c r="K102" s="3">
         <v>-307600</v>

--- a/AAII_Financials/Yearly/ERIC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ERIC_YR_FIN.xlsx
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>22397500</v>
+      </c>
+      <c r="E8" s="3">
         <v>26186700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>26050000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>25692400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>28296400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>24322300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>23724700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>25090100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>20802200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>23348800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>25164800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>26775800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>23673100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>25760100</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>12330800</v>
+      </c>
+      <c r="E9" s="3">
         <v>15805100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>15162600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>14520000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>16796000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>15206300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>15382300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>18594700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>14312800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>15018700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>15952900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>17469500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>16181800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>16710100</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>10066700</v>
+      </c>
+      <c r="E10" s="3">
         <v>10381600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>10887300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>11172400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>11500300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>9116100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>8342400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6495400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6489400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>8330100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>9211900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>9306300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>7491300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>9049900</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,53 +886,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>4643800</v>
+      </c>
+      <c r="E12" s="3">
         <v>4796100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>4526400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>4638000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>4785600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>4118100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>4204200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>4029000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2728000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3103700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3974100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3693400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3323800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3641400</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -963,81 +979,87 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>3850400</v>
+        <v>396500</v>
       </c>
       <c r="E14" s="3">
-        <v>279100</v>
+        <v>3844000</v>
       </c>
       <c r="F14" s="3">
+        <v>293100</v>
+      </c>
+      <c r="G14" s="3">
         <v>-33100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>179600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1153000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>988000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3121200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>706600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>476600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>160700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>524400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>159400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>237600</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>574800</v>
+      </c>
+      <c r="E15" s="3">
         <v>755000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>585700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>535100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>570500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>493000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>524600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>704900</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1053,9 +1075,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>24318400</v>
+        <v>21635100</v>
       </c>
       <c r="E17" s="3">
-        <v>23145800</v>
+        <v>24421200</v>
       </c>
       <c r="F17" s="3">
+        <v>23215100</v>
+      </c>
+      <c r="G17" s="3">
         <v>22153100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>24726400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>22002700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>22603500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>26216300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>20312500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>21286900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>23309600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>24674400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>22586200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>23728100</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>1868300</v>
+        <v>762300</v>
       </c>
       <c r="E18" s="3">
-        <v>2904200</v>
+        <v>1765500</v>
       </c>
       <c r="F18" s="3">
+        <v>2834900</v>
+      </c>
+      <c r="G18" s="3">
         <v>3539300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3570000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2319700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1121200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1126100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>489800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2061900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1855200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2101400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1086900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2032000</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1179,233 +1211,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>252300</v>
+        <v>96500</v>
       </c>
       <c r="E20" s="3">
-        <v>195300</v>
+        <v>155800</v>
       </c>
       <c r="F20" s="3">
+        <v>112000</v>
+      </c>
+      <c r="G20" s="3">
         <v>272200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-8000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>171100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>202200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>63400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-88600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-47800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>41900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>78300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>151500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>218800</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>2371100</v>
+        <v>1240600</v>
       </c>
       <c r="E21" s="3">
-        <v>3294500</v>
+        <v>2364700</v>
       </c>
       <c r="F21" s="3">
+        <v>3308500</v>
+      </c>
+      <c r="G21" s="3">
         <v>3802200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4148400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2641700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1443600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-484600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1243700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2953700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2983600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3371900</v>
       </c>
-      <c r="O21" s="3" t="s">
+      <c r="P21" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3277900</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>262700</v>
+      </c>
+      <c r="E22" s="3">
         <v>273100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>137800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>105200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>166000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>189800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>160900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>139800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>127900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>135000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>151900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>166300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>180200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>193700</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>233900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2318800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2360800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3234900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3313400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>937900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-164600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-4392800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>273300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1879100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1745200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2013500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1058200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2057100</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>200100</v>
+      </c>
+      <c r="E24" s="3">
         <v>276900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>527300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>693400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1167600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>741000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>541600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-430600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>177700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>586200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>515300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>579900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>441100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>630300</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>33800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2595700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1833500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2541400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2145800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>197000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-706200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3962200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>95600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1292900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1230000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1433600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>617100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1426800</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2629700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1796200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2509800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2128800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>238000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-734800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3979700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>78700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1281200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1276900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1413700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>600200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1384300</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1628,9 +1688,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1718,99 +1784,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-252300</v>
+        <v>-96500</v>
       </c>
       <c r="E32" s="3">
-        <v>-195300</v>
+        <v>-155800</v>
       </c>
       <c r="F32" s="3">
+        <v>-112000</v>
+      </c>
+      <c r="G32" s="3">
         <v>-272200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>8000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-171100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-202200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-63400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>88600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>47800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-41900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-78300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-151500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-218800</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2629700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1796200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2509800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2128800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>238000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-734800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3979700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>78700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1281200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1276900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1413700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>600200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1384300</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2629700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1796200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2509800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2128800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>238000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-734800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3979700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>78700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1281200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1276900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1413700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>600200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1384300</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1987,413 +2072,441 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>3965300</v>
+      </c>
+      <c r="E41" s="3">
         <v>3499200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3678900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5977600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5310300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4825500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4319700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4383800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6980700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2121100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3272800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3370100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4643800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4390500</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>1133600</v>
+      </c>
+      <c r="E42" s="3">
         <v>953000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>838100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1430200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>830400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>723500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>745500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>820100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1258100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4145400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>4692100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>5707900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>3328500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>4752600</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>6131600</v>
+      </c>
+      <c r="E43" s="3">
         <v>6921800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7364900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7700200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8210600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7411900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>9778300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>10418200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>16876900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8365800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>10287500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9880400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>8527800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9211600</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>2450900</v>
+      </c>
+      <c r="E44" s="3">
         <v>3587000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4398100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3888900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3421200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3303700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3291900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3121000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5847000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2688900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3110000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2680100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2993400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3754100</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E45" s="3">
         <v>196800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>152900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>82200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>240800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>59300</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L45" s="3">
         <v>660300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>600300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>911100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>841400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>591500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>460800</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>13942600</v>
+      </c>
+      <c r="E46" s="3">
         <v>15411400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>16673300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>19332300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>18239400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16475700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>18135400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>18743000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>16532700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>17921500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>22273500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>22479900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>20084900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>22569600</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>2046400</v>
+      </c>
+      <c r="E47" s="3">
         <v>1309800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1186200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3740800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2971700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2499600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2937800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3299400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1940600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>889400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1177200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1111400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>881500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1553100</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>1538900</v>
+      </c>
+      <c r="E48" s="3">
         <v>1841100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2120700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2380900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2601200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2391100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1445800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1570700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3160000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1503600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1472600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1346400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1194500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1224700</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>5785600</v>
+      </c>
+      <c r="E49" s="3">
         <v>7518500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10639800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4648700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4840100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3606500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3770600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3904800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11181200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5285500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6008400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5618000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5138900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4999900</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2481,54 +2597,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>466300</v>
+      </c>
+      <c r="E52" s="3">
         <v>631400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>656100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>687600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>589600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>601000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>738100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>720400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1605000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1289300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1471300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1144200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1280500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1478000</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>26417800</v>
+      </c>
+      <c r="E54" s="3">
         <v>29536200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>33531800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>33798900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>33062100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>29585400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>30242500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>31748600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>26829400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>26889400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>32402900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>31699800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>28580300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>31825200</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2655,278 +2784,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>2726300</v>
+      </c>
+      <c r="E57" s="3">
         <v>2761100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3687300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3946400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3894900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3254500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3362600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3215400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4830700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2117100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2701300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2414300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>11600</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>747600</v>
+      </c>
+      <c r="E58" s="3">
         <v>1977800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>813300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1316600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1246600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1272900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>253700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>310900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1517000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>224700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>251800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>870000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>495600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>881500</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>5425300</v>
+      </c>
+      <c r="E59" s="3">
         <v>5380100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5931700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5245900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5065100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4616600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8864300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8632700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11607000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5893500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8175800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7472300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9619100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10121700</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>11915600</v>
+      </c>
+      <c r="E60" s="3">
         <v>12867000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>13969600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>14040100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>13919900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>12504900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>12480700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>12159000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9517800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8235200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11129000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10756700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10123200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11014700</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>3367300</v>
+      </c>
+      <c r="E61" s="3">
         <v>3424400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3239100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3242600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3570300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3837800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3473700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3726100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1761200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2150700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2413300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2598600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2483700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2640000</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>407200</v>
+      </c>
+      <c r="E62" s="3">
         <v>565000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>451300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>587100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>519800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>513100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1104700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>778400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2779400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2568500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2821400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1667000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1580900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1679400</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>18016200</v>
+      </c>
+      <c r="E66" s="3">
         <v>19850300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>20743700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>21954500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>22690800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>20820800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>20366100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>19828800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14122200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13034000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>16474400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>15189400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>14354100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>15579900</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>3821600</v>
+      </c>
+      <c r="E72" s="3">
         <v>5017700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>8174400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7400700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>5839700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4160200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5019800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>6824900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>8799400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9954100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>11374500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>11652000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>9938400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>11579800</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>8519100</v>
+      </c>
+      <c r="E76" s="3">
         <v>9811700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12933000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12029800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10553600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8837500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9787300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11842100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>12707200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13855400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>15928500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>16510400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>14226300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>16245300</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2629700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1796200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2509800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2128800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>238000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-734800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3979700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>78700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1281200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1276900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1413700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>600200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1384300</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>545800</v>
+      </c>
+      <c r="E83" s="3">
         <v>666100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>629800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>658100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>729200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>648800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>368500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>501200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>839000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>966700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1095700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1195900</v>
       </c>
-      <c r="O83" s="3" t="s">
+      <c r="P83" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1025800</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>4180000</v>
+      </c>
+      <c r="E89" s="3">
         <v>713700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2960800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4320300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3522900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1806200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1051200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1172900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1322800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1947700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2064300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2047700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2289700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1133200</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-192600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-319200</v>
       </c>
-      <c r="E91" s="3">
-        <v>-425000</v>
-      </c>
       <c r="F91" s="3">
+        <v>-429500</v>
+      </c>
+      <c r="G91" s="3">
         <v>-405100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-547100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-539200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-447300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-473600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-578700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-788400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-587400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-530300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-564200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-566900</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-1441400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-866400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3299800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2198900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1850900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-379000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-465000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1963200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-782100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-755300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-829300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1308200</v>
       </c>
-      <c r="O94" s="3" t="s">
+      <c r="P94" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>515500</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -4221,53 +4453,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>812900</v>
+      </c>
+      <c r="E96" s="3">
         <v>894000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>798600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>736300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>607000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>353400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>369900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>399800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-1157900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1072000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1086800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1077900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-897100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-846300</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -4400,142 +4642,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-2156300</v>
+      </c>
+      <c r="E100" s="3">
         <v>100100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1528200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1029300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1521100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-738600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-458800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>669200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1108700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1012700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2011700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1119700</v>
       </c>
-      <c r="O100" s="3" t="s">
+      <c r="P100" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-737200</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>203400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-261500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>361000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>62300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-329600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>27600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>154400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-11100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>260300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-251900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>654400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>75500</v>
       </c>
-      <c r="O101" s="3" t="s">
+      <c r="P101" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-24600</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>785600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-314100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1506200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1154400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-178600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>716100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>281900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-132200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-307600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-72200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-122200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-304600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>624200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>886800</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/ERIC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ERIC_YR_FIN.xlsx
@@ -1111,7 +1111,7 @@
         <v>23215100</v>
       </c>
       <c r="G17" s="3">
-        <v>22153100</v>
+        <v>22211000</v>
       </c>
       <c r="H17" s="3">
         <v>24726400</v>
@@ -1159,7 +1159,7 @@
         <v>2834900</v>
       </c>
       <c r="G18" s="3">
-        <v>3539300</v>
+        <v>3481400</v>
       </c>
       <c r="H18" s="3">
         <v>3570000</v>
@@ -1227,7 +1227,7 @@
         <v>112000</v>
       </c>
       <c r="G20" s="3">
-        <v>272200</v>
+        <v>214200</v>
       </c>
       <c r="H20" s="3">
         <v>-8000</v>
@@ -1803,7 +1803,7 @@
         <v>-112000</v>
       </c>
       <c r="G32" s="3">
-        <v>-272200</v>
+        <v>-214200</v>
       </c>
       <c r="H32" s="3">
         <v>8000</v>

--- a/AAII_Financials/Yearly/ERIC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ERIC_YR_FIN.xlsx
@@ -656,219 +656,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>25678000</v>
+      </c>
+      <c r="E8" s="3">
         <v>22397500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>26186700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>26050000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>25692400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>28296400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>24322300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>23724700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>25090100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>20802200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>23348800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>25164800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>26775800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>23673100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>25760100</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>13315900</v>
+      </c>
+      <c r="E9" s="3">
         <v>12330800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>15805100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>15162600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>14520000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>16796000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>15206300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>15382300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>18594700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>14312800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>15018700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>15952900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>17469500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>16181800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>16710100</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>12362100</v>
+      </c>
+      <c r="E10" s="3">
         <v>10066700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>10381600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>10887300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>11172400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>11500300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>9116100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>8342400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6495400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6489400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>8330100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>9211900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>9306300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>7491300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>9049900</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -887,56 +899,60 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>4643800</v>
+        <v>5228900</v>
       </c>
       <c r="E12" s="3">
+        <v>4535400</v>
+      </c>
+      <c r="F12" s="3">
         <v>4796100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>4526400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>4638000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>4785600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>4118100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>4204200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>4029000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2728000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3103700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3974100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3693400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3323800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>3641400</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -982,87 +998,93 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>396500</v>
+        <v>-600300</v>
       </c>
       <c r="E14" s="3">
-        <v>3844000</v>
+        <v>1655800</v>
       </c>
       <c r="F14" s="3">
-        <v>293100</v>
+        <v>3850400</v>
       </c>
       <c r="G14" s="3">
+        <v>279100</v>
+      </c>
+      <c r="H14" s="3">
         <v>-33100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>179600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1153000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>988000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3121200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>706600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>476600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>160700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>524400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>159400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>237600</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>549800</v>
+      </c>
+      <c r="E15" s="3">
         <v>574800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>755000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>585700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>535100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>570500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>493000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>524600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>704900</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1078,9 +1100,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>21635100</v>
+        <v>22166600</v>
       </c>
       <c r="E17" s="3">
+        <v>20388200</v>
+      </c>
+      <c r="F17" s="3">
         <v>24421200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>23215100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>22211000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>24726400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>22002700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>22603500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>26216300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>20312500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>21286900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>23309600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>24674400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>22586200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>23728100</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>762300</v>
+        <v>3511500</v>
       </c>
       <c r="E18" s="3">
+        <v>2009200</v>
+      </c>
+      <c r="F18" s="3">
         <v>1765500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2834900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3481400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3570000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2319700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1121200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1126100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>489800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2061900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1855200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2101400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1086900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2032000</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1212,248 +1244,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>96500</v>
+        <v>-12900</v>
       </c>
       <c r="E20" s="3">
-        <v>155800</v>
+        <v>84100</v>
       </c>
       <c r="F20" s="3">
-        <v>112000</v>
+        <v>149500</v>
       </c>
       <c r="G20" s="3">
+        <v>126100</v>
+      </c>
+      <c r="H20" s="3">
         <v>214200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-8000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>171100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>202200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>63400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-88600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-47800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>41900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>78300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>151500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>218800</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>1240600</v>
+        <v>4074200</v>
       </c>
       <c r="E21" s="3">
-        <v>2364700</v>
+        <v>2499900</v>
       </c>
       <c r="F21" s="3">
-        <v>3308500</v>
+        <v>2371100</v>
       </c>
       <c r="G21" s="3">
+        <v>3294500</v>
+      </c>
+      <c r="H21" s="3">
         <v>3802200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4148400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2641700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1443600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-484600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1243700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2953700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2983600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3371900</v>
       </c>
-      <c r="P21" s="3" t="s">
+      <c r="Q21" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3277900</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>221100</v>
+      </c>
+      <c r="E22" s="3">
         <v>262700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>273100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>137800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>105200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>166000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>189800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>160900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>139800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>127900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>135000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>151900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>166300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>180200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>193700</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>4155500</v>
+      </c>
+      <c r="E23" s="3">
         <v>233900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2318800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2360800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3234900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3313400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>937900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-164600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-4392800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>273300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1879100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1745200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2013500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1058200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2057100</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>1040200</v>
+      </c>
+      <c r="E24" s="3">
         <v>200100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>276900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>527300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>693400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1167600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>741000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>541600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-430600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>177700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>586200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>515300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>579900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>441100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>630300</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>3115200</v>
+      </c>
+      <c r="E26" s="3">
         <v>33800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2595700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1833500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2541400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2145800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>197000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-706200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3962200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>95600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1292900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1230000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1433600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>617100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1426800</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>3084200</v>
+      </c>
+      <c r="E27" s="3">
         <v>1800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2629700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1796200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2509800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2128800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>238000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-734800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3979700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>78700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1281200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1276900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1413700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>600200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1384300</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1691,9 +1751,12 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1787,105 +1853,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-96500</v>
+        <v>12900</v>
       </c>
       <c r="E32" s="3">
-        <v>-155800</v>
+        <v>-84100</v>
       </c>
       <c r="F32" s="3">
-        <v>-112000</v>
+        <v>-149500</v>
       </c>
       <c r="G32" s="3">
+        <v>-126100</v>
+      </c>
+      <c r="H32" s="3">
         <v>-214200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>8000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-171100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-202200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-63400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>88600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>47800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-41900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-78300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-151500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-218800</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>3084200</v>
+      </c>
+      <c r="E33" s="3">
         <v>1800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2629700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1796200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2509800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2128800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>238000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-734800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3979700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>78700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1281200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1276900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1413700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>600200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1384300</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>3084200</v>
+      </c>
+      <c r="E35" s="3">
         <v>1800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2629700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1796200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2509800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2128800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>238000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-734800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3979700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>78700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1281200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1276900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1413700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>600200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1384300</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2073,440 +2158,468 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>4765600</v>
+      </c>
+      <c r="E41" s="3">
         <v>3965300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3499200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3678900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5977600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5310300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4825500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4319700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4383800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6980700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2121100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3272800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3370100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4643800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4390500</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>1379600</v>
+      </c>
+      <c r="E42" s="3">
         <v>1133600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>953000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>838100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1430200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>830400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>723500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>745500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>820100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1258100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>4145400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>4692100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>5707900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>3328500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>4752600</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>6302600</v>
+      </c>
+      <c r="E43" s="3">
         <v>6131600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6921800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7364900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7700200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8210600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7411900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>9778300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>10418200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>16876900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>8365800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>10287500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>9880400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>8527800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>9211600</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>2544300</v>
+      </c>
+      <c r="E44" s="3">
         <v>2450900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3587000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4398100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3888900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3421200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3303700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3291900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3121000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5847000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2688900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3110000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2680100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2993400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3754100</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>323100</v>
+      </c>
+      <c r="E45" s="3">
         <v>21000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>196800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>152900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>82200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>240800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>59300</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M45" s="3">
         <v>660300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>600300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>911100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>841400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>591500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>460800</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>15574500</v>
+      </c>
+      <c r="E46" s="3">
         <v>13942600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>15411400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>16673300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>19332300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>18239400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>16475700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>18135400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>18743000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>16532700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>17921500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>22273500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>22479900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>20084900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>22569600</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>4417200</v>
+      </c>
+      <c r="E47" s="3">
         <v>2046400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1309800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1186200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3740800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2971700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2499600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2937800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3299400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1940600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>889400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1177200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1111400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>881500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1553100</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>1684600</v>
+      </c>
+      <c r="E48" s="3">
         <v>1538900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1841100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2120700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2380900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2601200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2391100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1445800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1570700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3160000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1503600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1472600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1346400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1194500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1224700</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>5697300</v>
+      </c>
+      <c r="E49" s="3">
         <v>5785600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>7518500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10639800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4648700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4840100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3606500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3770600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3904800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11181200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5285500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>6008400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5618000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5138900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4999900</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2600,57 +2716,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>646600</v>
+      </c>
+      <c r="E52" s="3">
         <v>466300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>631400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>656100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>687600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>589600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>601000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>738100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>720400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1605000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1289300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1471300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1144200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1280500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1478000</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>30293500</v>
+      </c>
+      <c r="E54" s="3">
         <v>26417800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>29536200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>33531800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>33798900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>33062100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>29585400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>30242500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>31748600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>26829400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>26889400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>32402900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>31699800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>28580300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>31825200</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2785,296 +2914,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>2857100</v>
+      </c>
+      <c r="E57" s="3">
         <v>2726300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2761100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3687300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3946400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3894900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3254500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3362600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3215400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4830700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2117100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2701300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2414300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>11600</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>577900</v>
+      </c>
+      <c r="E58" s="3">
         <v>747600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1977800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>813300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1316600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1246600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1272900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>253700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>310900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1517000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>224700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>251800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>870000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>495600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>881500</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>5281100</v>
+      </c>
+      <c r="E59" s="3">
         <v>5425300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5380100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5931700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5245900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5065100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4616600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8864300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>8632700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11607000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5893500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8175800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7472300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>9619100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10121700</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>12035800</v>
+      </c>
+      <c r="E60" s="3">
         <v>11915600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12867000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>13969600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>14040100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>13919900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>12504900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>12480700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>12159000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>9517800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8235200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11129000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10756700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>10123200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>11014700</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>3790400</v>
+      </c>
+      <c r="E61" s="3">
         <v>3367300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3424400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3239100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3242600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3570300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3837800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3473700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3726100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1761200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2150700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2413300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2598600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2483700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2640000</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>464900</v>
+      </c>
+      <c r="E62" s="3">
         <v>407200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>565000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>451300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>587100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>519800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>513100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1104700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>778400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2779400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2568500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2821400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1667000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1580900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1679400</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>18330700</v>
+      </c>
+      <c r="E66" s="3">
         <v>18016200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>19850300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>20743700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>21954500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>22690800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>20820800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>20366100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>19828800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14122200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13034000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>16474400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>15189400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>14354100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>15579900</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -3428,9 +3595,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>7063500</v>
+      </c>
+      <c r="E72" s="3">
         <v>3821600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5017700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>8174400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7400700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5839700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4160200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5019800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6824900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>8799400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9954100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>11374500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>11652000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>9938400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>11579800</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>11883700</v>
+      </c>
+      <c r="E76" s="3">
         <v>8519100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9811700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12933000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12029800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>10553600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8837500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9787300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11842100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>12707200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13855400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>15928500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>16510400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>14226300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>16245300</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>3084200</v>
+      </c>
+      <c r="E81" s="3">
         <v>1800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2629700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1796200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2509800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2128800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>238000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-734800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3979700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>78700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1281200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1276900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1413700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>600200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1384300</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -3886,56 +4083,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>574800</v>
+      </c>
+      <c r="E83" s="3">
         <v>545800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>666100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>629800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>658100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>729200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>648800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>368500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>501200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>839000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>966700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1095700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1195900</v>
       </c>
-      <c r="P83" s="3" t="s">
+      <c r="Q83" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1025800</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>3575300</v>
+      </c>
+      <c r="E89" s="3">
         <v>4180000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>713700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2960800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4320300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3522900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1806200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1051200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1172900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1322800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1947700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2064300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2047700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2289700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1133200</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
-        <v>-192600</v>
+        <v>-285300</v>
       </c>
       <c r="E91" s="3">
-        <v>-319200</v>
+        <v>-211400</v>
       </c>
       <c r="F91" s="3">
+        <v>-327800</v>
+      </c>
+      <c r="G91" s="3">
         <v>-429500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-405100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-547100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-539200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-447300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-473600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-578700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-788400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-587400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-530300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-564200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-566900</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -4385,57 +4611,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-1240800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1441400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-866400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3299800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2198900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1850900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-379000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-465000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1963200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-782100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-755300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-829300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1308200</v>
       </c>
-      <c r="P94" s="3" t="s">
+      <c r="Q94" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>515500</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -4454,56 +4686,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>1030600</v>
+      </c>
+      <c r="E96" s="3">
         <v>812900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>894000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>798600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>736300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>607000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>353400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>369900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>399800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1157900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1072000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1086800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1077900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-897100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-846300</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -4645,151 +4887,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-1543100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2156300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>100100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1528200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1029300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1521100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-738600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-458800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>669200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1108700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1012700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2011700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1119700</v>
       </c>
-      <c r="P100" s="3" t="s">
+      <c r="Q100" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-737200</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-786900</v>
+      </c>
+      <c r="E101" s="3">
         <v>203400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-261500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>361000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>62300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-329600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>27600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>154400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-11100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>260300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-251900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>654400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>75500</v>
       </c>
-      <c r="P101" s="3" t="s">
+      <c r="Q101" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-24600</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E102" s="3">
         <v>785600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-314100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1506200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1154400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-178600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>716100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>281900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-132200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-307600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-72200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-122200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-304600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>624200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>886800</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
